--- a/data/proc_data/private_data/2025_b_municipal.xlsx
+++ b/data/proc_data/private_data/2025_b_municipal.xlsx
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.788</v>
+        <v>0.7877374735446694</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -900,7 +900,7 @@
         <v>0.75</v>
       </c>
       <c r="AR2">
-        <v>0.724</v>
+        <v>0.7236047944033869</v>
       </c>
       <c r="AS2">
         <v>10</v>
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.769</v>
+        <v>0.7691746312271031</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1149,7 +1149,7 @@
         <v>0.7</v>
       </c>
       <c r="AR3">
-        <v>0.732</v>
+        <v>0.732348369263375</v>
       </c>
       <c r="AS3">
         <v>7</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.769</v>
+        <v>0.7691746312271031</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1398,7 +1398,7 @@
         <v>0.7</v>
       </c>
       <c r="AR4">
-        <v>0.62</v>
+        <v>0.6203692526354563</v>
       </c>
       <c r="AS4">
         <v>45</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.753</v>
+        <v>0.7532636235263321</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1644,7 +1644,7 @@
         <v>0.8</v>
       </c>
       <c r="AR5">
-        <v>0.694</v>
+        <v>0.6944595448700931</v>
       </c>
       <c r="AS5">
         <v>17</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.743</v>
+        <v>0.7426562850591515</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1893,7 +1893,7 @@
         <v>0.7</v>
       </c>
       <c r="AR6">
-        <v>0.476</v>
+        <v>0.4758701733703886</v>
       </c>
       <c r="AS6">
         <v>180</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.743</v>
+        <v>0.7426562850591515</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -2142,7 +2142,7 @@
         <v>0.7</v>
       </c>
       <c r="AR7">
-        <v>0.5659999999999999</v>
+        <v>0.5662204469235997</v>
       </c>
       <c r="AS7">
         <v>85</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.716</v>
+        <v>0.7161379388911997</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -2391,7 +2391,7 @@
         <v>0.7</v>
       </c>
       <c r="AR8">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS8">
         <v>62</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.7</v>
+        <v>0.7002269311904288</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -2640,7 +2640,7 @@
         <v>0.8</v>
       </c>
       <c r="AR9">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS9">
         <v>109</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.698</v>
+        <v>0.6975750965736336</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2889,7 +2889,7 @@
         <v>0.65</v>
       </c>
       <c r="AR10">
-        <v>0.674</v>
+        <v>0.6740578701967872</v>
       </c>
       <c r="AS10">
         <v>22</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.698</v>
+        <v>0.6975750965736336</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -3138,7 +3138,7 @@
         <v>0.65</v>
       </c>
       <c r="AR11">
-        <v>0.654</v>
+        <v>0.6536561955234815</v>
       </c>
       <c r="AS11">
         <v>32</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.696</v>
+        <v>0.6963189643867307</v>
       </c>
       <c r="E12">
         <v>11</v>
@@ -3384,7 +3384,7 @@
         <v>0.7894736842105263</v>
       </c>
       <c r="AR12">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS12">
         <v>61</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.6899999999999999</v>
+        <v>0.6896195927232481</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -3633,7 +3633,7 @@
         <v>0.7</v>
       </c>
       <c r="AR13">
-        <v>0.744</v>
+        <v>0.7440064690766927</v>
       </c>
       <c r="AS13">
         <v>3</v>
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.6899999999999999</v>
+        <v>0.6896195927232481</v>
       </c>
       <c r="E14">
         <v>13</v>
@@ -3882,7 +3882,7 @@
         <v>0.7</v>
       </c>
       <c r="AR14">
-        <v>0.694</v>
+        <v>0.6944595448700931</v>
       </c>
       <c r="AS14">
         <v>19</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.6899999999999999</v>
+        <v>0.6896195927232481</v>
       </c>
       <c r="E15">
         <v>14</v>
@@ -4131,7 +4131,7 @@
         <v>0.7</v>
       </c>
       <c r="AR15">
-        <v>0.627</v>
+        <v>0.627425470943517</v>
       </c>
       <c r="AS15">
         <v>41</v>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.6899999999999999</v>
+        <v>0.6896195927232481</v>
       </c>
       <c r="E16">
         <v>15</v>
@@ -4380,7 +4380,7 @@
         <v>0.7</v>
       </c>
       <c r="AR16">
-        <v>0.756</v>
+        <v>0.7556645688900103</v>
       </c>
       <c r="AS16">
         <v>1</v>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.6870000000000001</v>
+        <v>0.6869677581064531</v>
       </c>
       <c r="E17">
         <v>16</v>
@@ -4629,7 +4629,7 @@
         <v>0.55</v>
       </c>
       <c r="AR17">
-        <v>0.636</v>
+        <v>0.6361690458035052</v>
       </c>
       <c r="AS17">
         <v>39</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.679</v>
+        <v>0.6790122542560675</v>
       </c>
       <c r="E18">
         <v>17</v>
@@ -4878,7 +4878,7 @@
         <v>0.6</v>
       </c>
       <c r="AR18">
-        <v>0.724</v>
+        <v>0.7236047944033869</v>
       </c>
       <c r="AS18">
         <v>12</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.679</v>
+        <v>0.6790122542560675</v>
       </c>
       <c r="E19">
         <v>18</v>
@@ -5127,7 +5127,7 @@
         <v>0.6</v>
       </c>
       <c r="AR19">
-        <v>0.715</v>
+        <v>0.7148612195433988</v>
       </c>
       <c r="AS19">
         <v>15</v>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.674</v>
+        <v>0.6737085850224771</v>
       </c>
       <c r="E20">
         <v>19</v>
@@ -5376,7 +5376,7 @@
         <v>0.8</v>
       </c>
       <c r="AR20">
-        <v>0.517</v>
+        <v>0.5166735227170001</v>
       </c>
       <c r="AS20">
         <v>136</v>
@@ -5511,7 +5511,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.671</v>
+        <v>0.671056750405682</v>
       </c>
       <c r="E21">
         <v>20</v>
@@ -5625,7 +5625,7 @@
         <v>0.65</v>
       </c>
       <c r="AR21">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS21">
         <v>114</v>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.671</v>
+        <v>0.671056750405682</v>
       </c>
       <c r="E22">
         <v>21</v>
@@ -5874,7 +5874,7 @@
         <v>0.65</v>
       </c>
       <c r="AR22">
-        <v>0.636</v>
+        <v>0.6361690458035052</v>
       </c>
       <c r="AS22">
         <v>38</v>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.671</v>
+        <v>0.671056750405682</v>
       </c>
       <c r="E23">
         <v>22</v>
@@ -6123,7 +6123,7 @@
         <v>0.65</v>
       </c>
       <c r="AR23">
-        <v>0.633</v>
+        <v>0.6332545208501759</v>
       </c>
       <c r="AS23">
         <v>40</v>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.666</v>
+        <v>0.6657530811720915</v>
       </c>
       <c r="E24">
         <v>23</v>
@@ -6372,7 +6372,7 @@
         <v>0.85</v>
       </c>
       <c r="AR24">
-        <v>0.619</v>
+        <v>0.6186818960835287</v>
       </c>
       <c r="AS24">
         <v>46</v>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.663</v>
+        <v>0.6631012465552965</v>
       </c>
       <c r="E25">
         <v>24</v>
@@ -6621,7 +6621,7 @@
         <v>0.7</v>
       </c>
       <c r="AR25">
-        <v>0.625</v>
+        <v>0.6245109459901875</v>
       </c>
       <c r="AS25">
         <v>44</v>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.66</v>
+        <v>0.6604494119385013</v>
       </c>
       <c r="E26">
         <v>25</v>
@@ -6870,7 +6870,7 @@
         <v>0.55</v>
       </c>
       <c r="AR26">
-        <v>0.694</v>
+        <v>0.6944595448700931</v>
       </c>
       <c r="AS26">
         <v>18</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.66</v>
+        <v>0.6604494119385013</v>
       </c>
       <c r="E27">
         <v>26</v>
@@ -7119,7 +7119,7 @@
         <v>0.55</v>
       </c>
       <c r="AR27">
-        <v>0.587</v>
+        <v>0.5866221215969055</v>
       </c>
       <c r="AS27">
         <v>70</v>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.66</v>
+        <v>0.6604494119385013</v>
       </c>
       <c r="E28">
         <v>27</v>
@@ -7368,7 +7368,7 @@
         <v>0.55</v>
       </c>
       <c r="AR28">
-        <v>0.662</v>
+        <v>0.6623997703834696</v>
       </c>
       <c r="AS28">
         <v>27</v>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.655</v>
+        <v>0.655145742704911</v>
       </c>
       <c r="E29">
         <v>28</v>
@@ -7617,7 +7617,7 @@
         <v>0.75</v>
       </c>
       <c r="AR29">
-        <v>0.625</v>
+        <v>0.6245109459901875</v>
       </c>
       <c r="AS29">
         <v>43</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.655</v>
+        <v>0.655145742704911</v>
       </c>
       <c r="E30">
         <v>29</v>
@@ -7866,7 +7866,7 @@
         <v>0.75</v>
       </c>
       <c r="AR30">
-        <v>0.5570000000000001</v>
+        <v>0.5574768720636116</v>
       </c>
       <c r="AS30">
         <v>90</v>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.652</v>
+        <v>0.6524939080881158</v>
       </c>
       <c r="E31">
         <v>30</v>
@@ -8115,7 +8115,7 @@
         <v>0.6</v>
       </c>
       <c r="AR31">
-        <v>0.724</v>
+        <v>0.7236047944033869</v>
       </c>
       <c r="AS31">
         <v>11</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.65</v>
+        <v>0.6498420734713206</v>
       </c>
       <c r="E32">
         <v>31</v>
@@ -8364,7 +8364,7 @@
         <v>0.45</v>
       </c>
       <c r="AR32">
-        <v>0.654</v>
+        <v>0.6536561955234815</v>
       </c>
       <c r="AS32">
         <v>31</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.647</v>
+        <v>0.6471902388545254</v>
       </c>
       <c r="E33">
         <v>32</v>
@@ -8613,7 +8613,7 @@
         <v>0.8</v>
       </c>
       <c r="AR33">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS33">
         <v>204</v>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.645</v>
+        <v>0.6445384042377303</v>
       </c>
       <c r="E34">
         <v>33</v>
@@ -8862,7 +8862,7 @@
         <v>0.65</v>
       </c>
       <c r="AR34">
-        <v>0.665</v>
+        <v>0.6653142953367991</v>
       </c>
       <c r="AS34">
         <v>26</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.645</v>
+        <v>0.6445384042377303</v>
       </c>
       <c r="E35">
         <v>34</v>
@@ -9111,7 +9111,7 @@
         <v>0.65</v>
       </c>
       <c r="AR35">
-        <v>0.517</v>
+        <v>0.5166735227170001</v>
       </c>
       <c r="AS35">
         <v>135</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.645</v>
+        <v>0.6445384042377303</v>
       </c>
       <c r="E36">
         <v>35</v>
@@ -9360,7 +9360,7 @@
         <v>0.65</v>
       </c>
       <c r="AR36">
-        <v>0.636</v>
+        <v>0.6361690458035052</v>
       </c>
       <c r="AS36">
         <v>37</v>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>0.645</v>
+        <v>0.6445384042377303</v>
       </c>
       <c r="E37">
         <v>36</v>
@@ -9609,7 +9609,7 @@
         <v>0.65</v>
       </c>
       <c r="AR37">
-        <v>0.555</v>
+        <v>0.5545623471102822</v>
       </c>
       <c r="AS37">
         <v>96</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.645</v>
+        <v>0.6445384042377303</v>
       </c>
       <c r="E38">
         <v>37</v>
@@ -9858,7 +9858,7 @@
         <v>0.65</v>
       </c>
       <c r="AR38">
-        <v>0.499</v>
+        <v>0.4991863729970238</v>
       </c>
       <c r="AS38">
         <v>149</v>
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.642</v>
+        <v>0.6418865696209352</v>
       </c>
       <c r="E39">
         <v>38</v>
@@ -10107,7 +10107,7 @@
         <v>0.5</v>
       </c>
       <c r="AR39">
-        <v>0.584</v>
+        <v>0.5837075966435761</v>
       </c>
       <c r="AS39">
         <v>71</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.637</v>
+        <v>0.6365829003873448</v>
       </c>
       <c r="E40">
         <v>39</v>
@@ -10356,7 +10356,7 @@
         <v>0.7</v>
       </c>
       <c r="AR40">
-        <v>0.657</v>
+        <v>0.656570720476811</v>
       </c>
       <c r="AS40">
         <v>28</v>
@@ -10491,7 +10491,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.629</v>
+        <v>0.6286273965369593</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -10605,7 +10605,7 @@
         <v>0.75</v>
       </c>
       <c r="AR41">
-        <v>0.616</v>
+        <v>0.6157673711301994</v>
       </c>
       <c r="AS41">
         <v>52</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.629</v>
+        <v>0.6286273965369593</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -10854,7 +10854,7 @@
         <v>0.75</v>
       </c>
       <c r="AR42">
-        <v>0.645</v>
+        <v>0.6449126206634933</v>
       </c>
       <c r="AS42">
         <v>36</v>
@@ -10989,7 +10989,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.629</v>
+        <v>0.6286273965369593</v>
       </c>
       <c r="E43">
         <v>42</v>
@@ -11103,7 +11103,7 @@
         <v>0.75</v>
       </c>
       <c r="AR43">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS43">
         <v>79</v>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>0.626</v>
+        <v>0.625975561920164</v>
       </c>
       <c r="E44">
         <v>43</v>
@@ -11352,7 +11352,7 @@
         <v>0.6</v>
       </c>
       <c r="AR44">
-        <v>0.753</v>
+        <v>0.7527500439366809</v>
       </c>
       <c r="AS44">
         <v>2</v>
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.626</v>
+        <v>0.625975561920164</v>
       </c>
       <c r="E45">
         <v>44</v>
@@ -11601,7 +11601,7 @@
         <v>0.6</v>
       </c>
       <c r="AR45">
-        <v>0.744</v>
+        <v>0.7440064690766927</v>
       </c>
       <c r="AS45">
         <v>4</v>
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.626</v>
+        <v>0.625975561920164</v>
       </c>
       <c r="E46">
         <v>45</v>
@@ -11850,7 +11850,7 @@
         <v>0.6</v>
       </c>
       <c r="AR46">
-        <v>0.543</v>
+        <v>0.5429042472969646</v>
       </c>
       <c r="AS46">
         <v>105</v>
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>0.626</v>
+        <v>0.625975561920164</v>
       </c>
       <c r="E47">
         <v>46</v>
@@ -12099,7 +12099,7 @@
         <v>0.6</v>
       </c>
       <c r="AR47">
-        <v>0.587</v>
+        <v>0.5866221215969055</v>
       </c>
       <c r="AS47">
         <v>68</v>
@@ -12234,7 +12234,7 @@
         </is>
       </c>
       <c r="D48">
-        <v>0.618</v>
+        <v>0.6180200580697786</v>
       </c>
       <c r="E48">
         <v>47</v>
@@ -12348,7 +12348,7 @@
         <v>0.65</v>
       </c>
       <c r="AR48">
-        <v>0.616</v>
+        <v>0.6157673711301994</v>
       </c>
       <c r="AS48">
         <v>50</v>
@@ -12483,7 +12483,7 @@
         </is>
       </c>
       <c r="D49">
-        <v>0.618</v>
+        <v>0.6180200580697786</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -12597,7 +12597,7 @@
         <v>0.65</v>
       </c>
       <c r="AR49">
-        <v>0.616</v>
+        <v>0.6157673711301994</v>
       </c>
       <c r="AS49">
         <v>53</v>
@@ -12732,7 +12732,7 @@
         </is>
       </c>
       <c r="D50">
-        <v>0.618</v>
+        <v>0.6180200580697786</v>
       </c>
       <c r="E50">
         <v>49</v>
@@ -12846,7 +12846,7 @@
         <v>0.65</v>
       </c>
       <c r="AR50">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS50">
         <v>73</v>
@@ -12981,7 +12981,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>0.615</v>
+        <v>0.6153682234529834</v>
       </c>
       <c r="E51">
         <v>50</v>
@@ -13095,7 +13095,7 @@
         <v>0.5</v>
       </c>
       <c r="AR51">
-        <v>0.549</v>
+        <v>0.5487332972036234</v>
       </c>
       <c r="AS51">
         <v>102</v>
@@ -13230,7 +13230,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>0.615</v>
+        <v>0.6153682234529834</v>
       </c>
       <c r="E52">
         <v>51</v>
@@ -13344,7 +13344,7 @@
         <v>0.5</v>
       </c>
       <c r="AR52">
-        <v>0.735</v>
+        <v>0.7352628942167045</v>
       </c>
       <c r="AS52">
         <v>6</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.615</v>
+        <v>0.6153682234529834</v>
       </c>
       <c r="E53">
         <v>52</v>
@@ -13593,7 +13593,7 @@
         <v>0.5</v>
       </c>
       <c r="AR53">
-        <v>0.732</v>
+        <v>0.732348369263375</v>
       </c>
       <c r="AS53">
         <v>8</v>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>0.615</v>
+        <v>0.6153682234529834</v>
       </c>
       <c r="E54">
         <v>53</v>
@@ -13842,7 +13842,7 @@
         <v>0.5</v>
       </c>
       <c r="AR54">
-        <v>0.732</v>
+        <v>0.732348369263375</v>
       </c>
       <c r="AS54">
         <v>9</v>
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.61</v>
+        <v>0.6100645542193931</v>
       </c>
       <c r="E55">
         <v>54</v>
@@ -14091,7 +14091,7 @@
         <v>0.7</v>
       </c>
       <c r="AR55">
-        <v>0.6860000000000001</v>
+        <v>0.6857159700101048</v>
       </c>
       <c r="AS55">
         <v>20</v>
@@ -14226,7 +14226,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>0.61</v>
+        <v>0.6100645542193931</v>
       </c>
       <c r="E56">
         <v>55</v>
@@ -14340,7 +14340,7 @@
         <v>0.7</v>
       </c>
       <c r="AR56">
-        <v>0.619</v>
+        <v>0.6186818960835287</v>
       </c>
       <c r="AS56">
         <v>47</v>
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>0.61</v>
+        <v>0.6100645542193931</v>
       </c>
       <c r="E57">
         <v>56</v>
@@ -14589,7 +14589,7 @@
         <v>0.7</v>
       </c>
       <c r="AR57">
-        <v>0.52</v>
+        <v>0.5195880476703295</v>
       </c>
       <c r="AS57">
         <v>132</v>
@@ -14724,7 +14724,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>0.61</v>
+        <v>0.6100645542193931</v>
       </c>
       <c r="E58">
         <v>57</v>
@@ -14838,7 +14838,7 @@
         <v>0.7</v>
       </c>
       <c r="AR58">
-        <v>0.627</v>
+        <v>0.627425470943517</v>
       </c>
       <c r="AS58">
         <v>42</v>
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>0.607</v>
+        <v>0.6074127196025979</v>
       </c>
       <c r="E59">
         <v>58</v>
@@ -15087,7 +15087,7 @@
         <v>0.55</v>
       </c>
       <c r="AR59">
-        <v>0.616</v>
+        <v>0.6157673711301994</v>
       </c>
       <c r="AS59">
         <v>51</v>
@@ -15222,7 +15222,7 @@
         </is>
       </c>
       <c r="D60">
-        <v>0.607</v>
+        <v>0.6074127196025979</v>
       </c>
       <c r="E60">
         <v>59</v>
@@ -15336,7 +15336,7 @@
         <v>0.55</v>
       </c>
       <c r="AR60">
-        <v>0.525</v>
+        <v>0.5254170975769883</v>
       </c>
       <c r="AS60">
         <v>129</v>
@@ -15471,7 +15471,7 @@
         </is>
       </c>
       <c r="D61">
-        <v>0.602</v>
+        <v>0.6021090503690076</v>
       </c>
       <c r="E61">
         <v>60</v>
@@ -15585,7 +15585,7 @@
         <v>0.75</v>
       </c>
       <c r="AR61">
-        <v>0.697</v>
+        <v>0.6973740698234223</v>
       </c>
       <c r="AS61">
         <v>16</v>
@@ -15720,7 +15720,7 @@
         </is>
       </c>
       <c r="D62">
-        <v>0.599</v>
+        <v>0.5994572157522124</v>
       </c>
       <c r="E62">
         <v>61</v>
@@ -15834,7 +15834,7 @@
         <v>0.6</v>
       </c>
       <c r="AR62">
-        <v>0.744</v>
+        <v>0.7440064690766927</v>
       </c>
       <c r="AS62">
         <v>5</v>
@@ -15969,7 +15969,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>0.599</v>
+        <v>0.5994572157522124</v>
       </c>
       <c r="E63">
         <v>62</v>
@@ -16083,7 +16083,7 @@
         <v>0.6</v>
       </c>
       <c r="AR63">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS63">
         <v>207</v>
@@ -16218,7 +16218,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>0.599</v>
+        <v>0.5994572157522124</v>
       </c>
       <c r="E64">
         <v>63</v>
@@ -16332,7 +16332,7 @@
         <v>0.6</v>
       </c>
       <c r="AR64">
-        <v>0.517</v>
+        <v>0.5166735227170001</v>
       </c>
       <c r="AS64">
         <v>137</v>
@@ -16467,7 +16467,7 @@
         </is>
       </c>
       <c r="D65">
-        <v>0.599</v>
+        <v>0.5994572157522124</v>
       </c>
       <c r="E65">
         <v>64</v>
@@ -16581,7 +16581,7 @@
         <v>0.6</v>
       </c>
       <c r="AR65">
-        <v>0.645</v>
+        <v>0.6449126206634933</v>
       </c>
       <c r="AS65">
         <v>35</v>
@@ -16716,7 +16716,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>0.599</v>
+        <v>0.5994572157522124</v>
       </c>
       <c r="E66">
         <v>65</v>
@@ -16830,7 +16830,7 @@
         <v>0.6</v>
       </c>
       <c r="AR66">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS66">
         <v>113</v>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="D67">
-        <v>0.594</v>
+        <v>0.5941535465186222</v>
       </c>
       <c r="E67">
         <v>66</v>
@@ -17079,7 +17079,7 @@
         <v>0.8</v>
       </c>
       <c r="AR67">
-        <v>0.616</v>
+        <v>0.6157673711301994</v>
       </c>
       <c r="AS67">
         <v>48</v>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="D68">
-        <v>0.592</v>
+        <v>0.5915017119018269</v>
       </c>
       <c r="E68">
         <v>67</v>
@@ -17328,7 +17328,7 @@
         <v>0.65</v>
       </c>
       <c r="AR68">
-        <v>0.657</v>
+        <v>0.656570720476811</v>
       </c>
       <c r="AS68">
         <v>29</v>
@@ -17463,7 +17463,7 @@
         </is>
       </c>
       <c r="D69">
-        <v>0.589</v>
+        <v>0.5888498772850318</v>
       </c>
       <c r="E69">
         <v>68</v>
@@ -17577,7 +17577,7 @@
         <v>0.5</v>
       </c>
       <c r="AR69">
-        <v>0.584</v>
+        <v>0.5837075966435761</v>
       </c>
       <c r="AS69">
         <v>72</v>
@@ -17712,7 +17712,7 @@
         </is>
       </c>
       <c r="D70">
-        <v>0.589</v>
+        <v>0.5888498772850318</v>
       </c>
       <c r="E70">
         <v>69</v>
@@ -17826,7 +17826,7 @@
         <v>0.5</v>
       </c>
       <c r="AR70">
-        <v>0.715</v>
+        <v>0.7148612195433988</v>
       </c>
       <c r="AS70">
         <v>13</v>
@@ -17961,7 +17961,7 @@
         </is>
       </c>
       <c r="D71">
-        <v>0.584</v>
+        <v>0.5835462080514414</v>
       </c>
       <c r="E71">
         <v>70</v>
@@ -18075,7 +18075,7 @@
         <v>0.7</v>
       </c>
       <c r="AR71">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS71">
         <v>214</v>
@@ -18210,7 +18210,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>0.584</v>
+        <v>0.5835462080514414</v>
       </c>
       <c r="E72">
         <v>71</v>
@@ -18324,7 +18324,7 @@
         <v>0.7</v>
       </c>
       <c r="AR72">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS72">
         <v>110</v>
@@ -18459,7 +18459,7 @@
         </is>
       </c>
       <c r="D73">
-        <v>0.584</v>
+        <v>0.5835462080514414</v>
       </c>
       <c r="E73">
         <v>72</v>
@@ -18573,7 +18573,7 @@
         <v>0.7</v>
       </c>
       <c r="AR73">
-        <v>0.648</v>
+        <v>0.6478271456168228</v>
       </c>
       <c r="AS73">
         <v>33</v>
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="D74">
-        <v>0.581</v>
+        <v>0.5808943734346463</v>
       </c>
       <c r="E74">
         <v>73</v>
@@ -18822,7 +18822,7 @@
         <v>0.55</v>
       </c>
       <c r="AR74">
-        <v>0.587</v>
+        <v>0.5866221215969055</v>
       </c>
       <c r="AS74">
         <v>67</v>
@@ -18957,7 +18957,7 @@
         </is>
       </c>
       <c r="D75">
-        <v>0.581</v>
+        <v>0.5808943734346463</v>
       </c>
       <c r="E75">
         <v>74</v>
@@ -19071,7 +19071,7 @@
         <v>0.55</v>
       </c>
       <c r="AR75">
-        <v>0.715</v>
+        <v>0.7148612195433988</v>
       </c>
       <c r="AS75">
         <v>14</v>
@@ -19206,7 +19206,7 @@
         </is>
       </c>
       <c r="D76">
-        <v>0.576</v>
+        <v>0.5755907042010558</v>
       </c>
       <c r="E76">
         <v>75</v>
@@ -19320,7 +19320,7 @@
         <v>0.75</v>
       </c>
       <c r="AR76">
-        <v>0.49</v>
+        <v>0.4904427981370356</v>
       </c>
       <c r="AS76">
         <v>156</v>
@@ -19455,7 +19455,7 @@
         </is>
       </c>
       <c r="D77">
-        <v>0.576</v>
+        <v>0.5755907042010558</v>
       </c>
       <c r="E77">
         <v>76</v>
@@ -19569,7 +19569,7 @@
         <v>0.75</v>
       </c>
       <c r="AR77">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS77">
         <v>170</v>
@@ -19704,7 +19704,7 @@
         </is>
       </c>
       <c r="D78">
-        <v>0.576</v>
+        <v>0.5755907042010558</v>
       </c>
       <c r="E78">
         <v>77</v>
@@ -19818,7 +19818,7 @@
         <v>0.75</v>
       </c>
       <c r="AR78">
-        <v>0.49</v>
+        <v>0.4904427981370356</v>
       </c>
       <c r="AS78">
         <v>159</v>
@@ -19953,7 +19953,7 @@
         </is>
       </c>
       <c r="D79">
-        <v>0.573</v>
+        <v>0.5729388695842608</v>
       </c>
       <c r="E79">
         <v>78</v>
@@ -20067,7 +20067,7 @@
         <v>0.6</v>
       </c>
       <c r="AR79">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS79">
         <v>80</v>
@@ -20202,7 +20202,7 @@
         </is>
       </c>
       <c r="D80">
-        <v>0.573</v>
+        <v>0.5729388695842608</v>
       </c>
       <c r="E80">
         <v>79</v>
@@ -20316,7 +20316,7 @@
         <v>0.6</v>
       </c>
       <c r="AR80">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS80">
         <v>233</v>
@@ -20451,7 +20451,7 @@
         </is>
       </c>
       <c r="D81">
-        <v>0.573</v>
+        <v>0.5729388695842608</v>
       </c>
       <c r="E81">
         <v>80</v>
@@ -20565,7 +20565,7 @@
         <v>0.6</v>
       </c>
       <c r="AR81">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS81">
         <v>235</v>
@@ -20700,7 +20700,7 @@
         </is>
       </c>
       <c r="D82">
-        <v>0.573</v>
+        <v>0.5729388695842608</v>
       </c>
       <c r="E82">
         <v>81</v>
@@ -20814,7 +20814,7 @@
         <v>0.6</v>
       </c>
       <c r="AR82">
-        <v>0.467</v>
+        <v>0.4671265985104004</v>
       </c>
       <c r="AS82">
         <v>194</v>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="D83">
-        <v>0.573</v>
+        <v>0.5729388695842608</v>
       </c>
       <c r="E83">
         <v>82</v>
@@ -21063,7 +21063,7 @@
         <v>0.6</v>
       </c>
       <c r="AR83">
-        <v>0.616</v>
+        <v>0.6157673711301994</v>
       </c>
       <c r="AS83">
         <v>49</v>
@@ -21198,7 +21198,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>0.573</v>
+        <v>0.5729388695842608</v>
       </c>
       <c r="E84">
         <v>83</v>
@@ -21312,7 +21312,7 @@
         <v>0.6</v>
       </c>
       <c r="AR84">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS84">
         <v>144</v>
@@ -21447,7 +21447,7 @@
         </is>
       </c>
       <c r="D85">
-        <v>0.571</v>
+        <v>0.5711709798397306</v>
       </c>
       <c r="E85">
         <v>84</v>
@@ -21555,7 +21555,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="AR85">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS85">
         <v>147</v>
@@ -21690,7 +21690,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>0.57</v>
+        <v>0.5702870349674656</v>
       </c>
       <c r="E86">
         <v>85</v>
@@ -21804,7 +21804,7 @@
         <v>0.45</v>
       </c>
       <c r="AR86">
-        <v>0.517</v>
+        <v>0.5166735227170001</v>
       </c>
       <c r="AS86">
         <v>139</v>
@@ -21939,7 +21939,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>0.5649999999999999</v>
+        <v>0.5649833657338752</v>
       </c>
       <c r="E87">
         <v>86</v>
@@ -22053,7 +22053,7 @@
         <v>0.65</v>
       </c>
       <c r="AR87">
-        <v>0.5659999999999999</v>
+        <v>0.5662204469235997</v>
       </c>
       <c r="AS87">
         <v>88</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="D88">
-        <v>0.5649999999999999</v>
+        <v>0.5649833657338752</v>
       </c>
       <c r="E88">
         <v>87</v>
@@ -22302,7 +22302,7 @@
         <v>0.65</v>
       </c>
       <c r="AR88">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS88">
         <v>263</v>
@@ -22437,7 +22437,7 @@
         </is>
       </c>
       <c r="D89">
-        <v>0.5620000000000001</v>
+        <v>0.5623315311170801</v>
       </c>
       <c r="E89">
         <v>88</v>
@@ -22551,7 +22551,7 @@
         <v>0.5</v>
       </c>
       <c r="AR89">
-        <v>0.674</v>
+        <v>0.6740578701967872</v>
       </c>
       <c r="AS89">
         <v>24</v>
@@ -22686,7 +22686,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>0.5620000000000001</v>
+        <v>0.5623315311170801</v>
       </c>
       <c r="E90">
         <v>89</v>
@@ -22800,7 +22800,7 @@
         <v>0.5</v>
       </c>
       <c r="AR90">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS90">
         <v>119</v>
@@ -22935,7 +22935,7 @@
         </is>
       </c>
       <c r="D91">
-        <v>0.5570000000000001</v>
+        <v>0.5570278618834897</v>
       </c>
       <c r="E91">
         <v>90</v>
@@ -23049,7 +23049,7 @@
         <v>0.7</v>
       </c>
       <c r="AR91">
-        <v>0.5659999999999999</v>
+        <v>0.5662204469235997</v>
       </c>
       <c r="AS91">
         <v>89</v>
@@ -23184,7 +23184,7 @@
         </is>
       </c>
       <c r="D92">
-        <v>0.5570000000000001</v>
+        <v>0.5570278618834897</v>
       </c>
       <c r="E92">
         <v>91</v>
@@ -23298,7 +23298,7 @@
         <v>0.7</v>
       </c>
       <c r="AR92">
-        <v>0.52</v>
+        <v>0.5195880476703295</v>
       </c>
       <c r="AS92">
         <v>131</v>
@@ -23433,7 +23433,7 @@
         </is>
       </c>
       <c r="D93">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E93">
         <v>92</v>
@@ -23547,7 +23547,7 @@
         <v>0.55</v>
       </c>
       <c r="AR93">
-        <v>0.607</v>
+        <v>0.6070237962702113</v>
       </c>
       <c r="AS93">
         <v>56</v>
@@ -23682,7 +23682,7 @@
         </is>
       </c>
       <c r="D94">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E94">
         <v>93</v>
@@ -23796,7 +23796,7 @@
         <v>0.55</v>
       </c>
       <c r="AR94">
-        <v>0.587</v>
+        <v>0.5866221215969055</v>
       </c>
       <c r="AS94">
         <v>69</v>
@@ -23931,7 +23931,7 @@
         </is>
       </c>
       <c r="D95">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E95">
         <v>94</v>
@@ -24045,7 +24045,7 @@
         <v>0.55</v>
       </c>
       <c r="AR95">
-        <v>0.476</v>
+        <v>0.4758701733703886</v>
       </c>
       <c r="AS95">
         <v>182</v>
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="D96">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E96">
         <v>95</v>
@@ -24315,7 +24315,7 @@
         </is>
       </c>
       <c r="D97">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E97">
         <v>96</v>
@@ -24429,7 +24429,7 @@
         <v>0.55</v>
       </c>
       <c r="AR97">
-        <v>0.555</v>
+        <v>0.5545623471102822</v>
       </c>
       <c r="AS97">
         <v>98</v>
@@ -24564,7 +24564,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E98">
         <v>97</v>
@@ -24678,7 +24678,7 @@
         <v>0.55</v>
       </c>
       <c r="AR98">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS98">
         <v>65</v>
@@ -24813,7 +24813,7 @@
         </is>
       </c>
       <c r="D99">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E99">
         <v>98</v>
@@ -24927,7 +24927,7 @@
         <v>0.55</v>
       </c>
       <c r="AR99">
-        <v>0.546</v>
+        <v>0.545818772250294</v>
       </c>
       <c r="AS99">
         <v>104</v>
@@ -25062,7 +25062,7 @@
         </is>
       </c>
       <c r="D100">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E100">
         <v>99</v>
@@ -25176,7 +25176,7 @@
         <v>0.55</v>
       </c>
       <c r="AR100">
-        <v>0.499</v>
+        <v>0.4991863729970238</v>
       </c>
       <c r="AS100">
         <v>152</v>
@@ -25311,7 +25311,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E101">
         <v>100</v>
@@ -25425,7 +25425,7 @@
         <v>0.55</v>
       </c>
       <c r="AR101">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS101">
         <v>213</v>
@@ -25560,7 +25560,7 @@
         </is>
       </c>
       <c r="D102">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E102">
         <v>101</v>
@@ -25674,7 +25674,7 @@
         <v>0.55</v>
       </c>
       <c r="AR102">
-        <v>0.52</v>
+        <v>0.5195880476703295</v>
       </c>
       <c r="AS102">
         <v>130</v>
@@ -25809,7 +25809,7 @@
         </is>
       </c>
       <c r="D103">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E103">
         <v>102</v>
@@ -25923,7 +25923,7 @@
         <v>0.55</v>
       </c>
       <c r="AR103">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS103">
         <v>74</v>
@@ -26058,7 +26058,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>0.554</v>
+        <v>0.5543760272666947</v>
       </c>
       <c r="E104">
         <v>103</v>
@@ -26172,7 +26172,7 @@
         <v>0.55</v>
       </c>
       <c r="AR104">
-        <v>0.5570000000000001</v>
+        <v>0.5574768720636116</v>
       </c>
       <c r="AS104">
         <v>91</v>
@@ -26307,7 +26307,7 @@
         </is>
       </c>
       <c r="D105">
-        <v>0.552</v>
+        <v>0.5517241926498995</v>
       </c>
       <c r="E105">
         <v>104</v>
@@ -26421,7 +26421,7 @@
         <v>0.4</v>
       </c>
       <c r="AR105">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS105">
         <v>64</v>
@@ -26556,7 +26556,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>0.551</v>
+        <v>0.5511659116779426</v>
       </c>
       <c r="E106">
         <v>105</v>
@@ -26667,7 +26667,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="AR106">
-        <v>0.418</v>
+        <v>0.4175796743038008</v>
       </c>
       <c r="AS106">
         <v>269</v>
@@ -26802,7 +26802,7 @@
         </is>
       </c>
       <c r="D107">
-        <v>0.549</v>
+        <v>0.5490723580331043</v>
       </c>
       <c r="E107">
         <v>106</v>
@@ -26916,7 +26916,7 @@
         <v>0.75</v>
       </c>
       <c r="AR107">
-        <v>0.61</v>
+        <v>0.6099383212235406</v>
       </c>
       <c r="AS107">
         <v>54</v>
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="D108">
-        <v>0.546</v>
+        <v>0.5464205234163091</v>
       </c>
       <c r="E108">
         <v>107</v>
@@ -27165,7 +27165,7 @@
         <v>0.6</v>
       </c>
       <c r="AR108">
-        <v>0.575</v>
+        <v>0.574964021783588</v>
       </c>
       <c r="AS108">
         <v>83</v>
@@ -27300,7 +27300,7 @@
         </is>
       </c>
       <c r="D109">
-        <v>0.546</v>
+        <v>0.5464205234163091</v>
       </c>
       <c r="E109">
         <v>108</v>
@@ -27414,7 +27414,7 @@
         <v>0.6</v>
       </c>
       <c r="AR109">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS109">
         <v>230</v>
@@ -27549,7 +27549,7 @@
         </is>
       </c>
       <c r="D110">
-        <v>0.546</v>
+        <v>0.5464205234163091</v>
       </c>
       <c r="E110">
         <v>109</v>
@@ -27663,7 +27663,7 @@
         <v>0.6</v>
       </c>
       <c r="AR110">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS110">
         <v>78</v>
@@ -27798,7 +27798,7 @@
         </is>
       </c>
       <c r="D111">
-        <v>0.546</v>
+        <v>0.5464205234163091</v>
       </c>
       <c r="E111">
         <v>110</v>
@@ -27912,7 +27912,7 @@
         <v>0.6</v>
       </c>
       <c r="AR111">
-        <v>0.549</v>
+        <v>0.5487332972036234</v>
       </c>
       <c r="AS111">
         <v>101</v>
@@ -28047,7 +28047,7 @@
         </is>
       </c>
       <c r="D112">
-        <v>0.546</v>
+        <v>0.5464205234163091</v>
       </c>
       <c r="E112">
         <v>111</v>
@@ -28161,7 +28161,7 @@
         <v>0.6</v>
       </c>
       <c r="AR112">
-        <v>0.496</v>
+        <v>0.4962718480436943</v>
       </c>
       <c r="AS112">
         <v>155</v>
@@ -28296,7 +28296,7 @@
         </is>
       </c>
       <c r="D113">
-        <v>0.544</v>
+        <v>0.5437686887995139</v>
       </c>
       <c r="E113">
         <v>112</v>
@@ -28410,7 +28410,7 @@
         <v>0.45</v>
       </c>
       <c r="AR113">
-        <v>0.54</v>
+        <v>0.5399897223436352</v>
       </c>
       <c r="AS113">
         <v>106</v>
@@ -28545,7 +28545,7 @@
         </is>
       </c>
       <c r="D114">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E114">
         <v>113</v>
@@ -28659,7 +28659,7 @@
         <v>0.65</v>
       </c>
       <c r="AR114">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS114">
         <v>222</v>
@@ -28794,7 +28794,7 @@
         </is>
       </c>
       <c r="D115">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E115">
         <v>114</v>
@@ -28908,7 +28908,7 @@
         <v>0.65</v>
       </c>
       <c r="AR115">
-        <v>0.607</v>
+        <v>0.6070237962702113</v>
       </c>
       <c r="AS115">
         <v>58</v>
@@ -29043,7 +29043,7 @@
         </is>
       </c>
       <c r="D116">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E116">
         <v>115</v>
@@ -29157,7 +29157,7 @@
         <v>0.65</v>
       </c>
       <c r="AR116">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS116">
         <v>205</v>
@@ -29292,7 +29292,7 @@
         </is>
       </c>
       <c r="D117">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E117">
         <v>116</v>
@@ -29406,7 +29406,7 @@
         <v>0.65</v>
       </c>
       <c r="AR117">
-        <v>0.517</v>
+        <v>0.5166735227170001</v>
       </c>
       <c r="AS117">
         <v>138</v>
@@ -29541,7 +29541,7 @@
         </is>
       </c>
       <c r="D118">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E118">
         <v>117</v>
@@ -29655,7 +29655,7 @@
         <v>0.65</v>
       </c>
       <c r="AR118">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS118">
         <v>122</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="D119">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E119">
         <v>118</v>
@@ -29904,7 +29904,7 @@
         <v>0.65</v>
       </c>
       <c r="AR119">
-        <v>0.499</v>
+        <v>0.4991863729970238</v>
       </c>
       <c r="AS119">
         <v>151</v>
@@ -30039,7 +30039,7 @@
         </is>
       </c>
       <c r="D120">
-        <v>0.538</v>
+        <v>0.5384650195659236</v>
       </c>
       <c r="E120">
         <v>119</v>
@@ -30153,7 +30153,7 @@
         <v>0.65</v>
       </c>
       <c r="AR120">
-        <v>0.5570000000000001</v>
+        <v>0.5574768720636116</v>
       </c>
       <c r="AS120">
         <v>92</v>
@@ -30288,7 +30288,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>0.536</v>
+        <v>0.5358131849491284</v>
       </c>
       <c r="E121">
         <v>120</v>
@@ -30402,7 +30402,7 @@
         <v>0.5</v>
       </c>
       <c r="AR121">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS121">
         <v>210</v>
@@ -30537,7 +30537,7 @@
         </is>
       </c>
       <c r="D122">
-        <v>0.536</v>
+        <v>0.5358131849491284</v>
       </c>
       <c r="E122">
         <v>121</v>
@@ -30651,7 +30651,7 @@
         <v>0.5</v>
       </c>
       <c r="AR122">
-        <v>0.665</v>
+        <v>0.6653142953367991</v>
       </c>
       <c r="AS122">
         <v>25</v>
@@ -30786,7 +30786,7 @@
         </is>
       </c>
       <c r="D123">
-        <v>0.531</v>
+        <v>0.5305095157155381</v>
       </c>
       <c r="E123">
         <v>122</v>
@@ -30900,7 +30900,7 @@
         <v>0.7</v>
       </c>
       <c r="AR123">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS123">
         <v>215</v>
@@ -31035,7 +31035,7 @@
         </is>
       </c>
       <c r="D124">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E124">
         <v>123</v>
@@ -31149,7 +31149,7 @@
         <v>0.55</v>
       </c>
       <c r="AR124">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS124">
         <v>146</v>
@@ -31284,7 +31284,7 @@
         </is>
       </c>
       <c r="D125">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E125">
         <v>124</v>
@@ -31398,7 +31398,7 @@
         <v>0.55</v>
       </c>
       <c r="AR125">
-        <v>0.674</v>
+        <v>0.6740578701967872</v>
       </c>
       <c r="AS125">
         <v>23</v>
@@ -31533,7 +31533,7 @@
         </is>
       </c>
       <c r="D126">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E126">
         <v>125</v>
@@ -31647,7 +31647,7 @@
         <v>0.55</v>
       </c>
       <c r="AR126">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS126">
         <v>116</v>
@@ -31782,7 +31782,7 @@
         </is>
       </c>
       <c r="D127">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E127">
         <v>126</v>
@@ -31896,7 +31896,7 @@
         <v>0.55</v>
       </c>
       <c r="AR127">
-        <v>0.5570000000000001</v>
+        <v>0.5574768720636116</v>
       </c>
       <c r="AS127">
         <v>94</v>
@@ -32031,7 +32031,7 @@
         </is>
       </c>
       <c r="D128">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E128">
         <v>127</v>
@@ -32145,7 +32145,7 @@
         <v>0.55</v>
       </c>
       <c r="AR128">
-        <v>0.549</v>
+        <v>0.5487332972036234</v>
       </c>
       <c r="AS128">
         <v>103</v>
@@ -32280,7 +32280,7 @@
         </is>
       </c>
       <c r="D129">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E129">
         <v>128</v>
@@ -32394,7 +32394,7 @@
         <v>0.55</v>
       </c>
       <c r="AR129">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS129">
         <v>60</v>
@@ -32529,7 +32529,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>0.528</v>
+        <v>0.527857681098743</v>
       </c>
       <c r="E130">
         <v>129</v>
@@ -32643,7 +32643,7 @@
         <v>0.55</v>
       </c>
       <c r="AR130">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS130">
         <v>232</v>
@@ -32778,7 +32778,7 @@
         </is>
       </c>
       <c r="D131">
-        <v>0.525</v>
+        <v>0.5252058464819478</v>
       </c>
       <c r="E131">
         <v>130</v>
@@ -32892,7 +32892,7 @@
         <v>0.4</v>
       </c>
       <c r="AR131">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS131">
         <v>115</v>
@@ -33027,7 +33027,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>0.523</v>
+        <v>0.5225540118651526</v>
       </c>
       <c r="E132">
         <v>131</v>
@@ -33141,7 +33141,7 @@
         <v>0.75</v>
       </c>
       <c r="AR132">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS132">
         <v>301</v>
@@ -33276,7 +33276,7 @@
         </is>
       </c>
       <c r="D133">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E133">
         <v>132</v>
@@ -33390,7 +33390,7 @@
         <v>0.6</v>
       </c>
       <c r="AR133">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS133">
         <v>190</v>
@@ -33525,7 +33525,7 @@
         </is>
       </c>
       <c r="D134">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E134">
         <v>133</v>
@@ -33639,7 +33639,7 @@
         <v>0.6</v>
       </c>
       <c r="AR134">
-        <v>0.657</v>
+        <v>0.656570720476811</v>
       </c>
       <c r="AS134">
         <v>30</v>
@@ -33774,7 +33774,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E135">
         <v>134</v>
@@ -33888,7 +33888,7 @@
         <v>0.6</v>
       </c>
       <c r="AR135">
-        <v>0.476</v>
+        <v>0.4758701733703886</v>
       </c>
       <c r="AS135">
         <v>183</v>
@@ -34023,7 +34023,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E136">
         <v>135</v>
@@ -34137,7 +34137,7 @@
         <v>0.6</v>
       </c>
       <c r="AR136">
-        <v>0.418</v>
+        <v>0.4175796743038008</v>
       </c>
       <c r="AS136">
         <v>268</v>
@@ -34272,7 +34272,7 @@
         </is>
       </c>
       <c r="D137">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E137">
         <v>136</v>
@@ -34386,7 +34386,7 @@
         <v>0.6</v>
       </c>
       <c r="AR137">
-        <v>0.61</v>
+        <v>0.6099383212235406</v>
       </c>
       <c r="AS137">
         <v>55</v>
@@ -34521,7 +34521,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E138">
         <v>137</v>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E139">
         <v>138</v>
@@ -34770,7 +34770,7 @@
         <v>0.6</v>
       </c>
       <c r="AR139">
-        <v>0.52</v>
+        <v>0.5195880476703295</v>
       </c>
       <c r="AS139">
         <v>134</v>
@@ -34905,7 +34905,7 @@
         </is>
       </c>
       <c r="D140">
-        <v>0.52</v>
+        <v>0.5199021772483574</v>
       </c>
       <c r="E140">
         <v>139</v>
@@ -35019,7 +35019,7 @@
         <v>0.6</v>
       </c>
       <c r="AR140">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS140">
         <v>143</v>
@@ -35154,7 +35154,7 @@
         </is>
       </c>
       <c r="D141">
-        <v>0.517</v>
+        <v>0.5172503426315622</v>
       </c>
       <c r="E141">
         <v>140</v>
@@ -35268,7 +35268,7 @@
         <v>0.45</v>
       </c>
       <c r="AR141">
-        <v>0.488</v>
+        <v>0.4875282731837062</v>
       </c>
       <c r="AS141">
         <v>164</v>
@@ -35403,7 +35403,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>0.517</v>
+        <v>0.5172503426315622</v>
       </c>
       <c r="E142">
         <v>141</v>
@@ -35517,7 +35517,7 @@
         <v>0.45</v>
       </c>
       <c r="AR142">
-        <v>0.674</v>
+        <v>0.6740578701967872</v>
       </c>
       <c r="AS142">
         <v>21</v>
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="D143">
-        <v>0.512</v>
+        <v>0.511946673397972</v>
       </c>
       <c r="E143">
         <v>142</v>
@@ -35766,7 +35766,7 @@
         <v>0.65</v>
       </c>
       <c r="AR143">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS143">
         <v>223</v>
@@ -35901,7 +35901,7 @@
         </is>
       </c>
       <c r="D144">
-        <v>0.512</v>
+        <v>0.511946673397972</v>
       </c>
       <c r="E144">
         <v>143</v>
@@ -36015,7 +36015,7 @@
         <v>0.65</v>
       </c>
       <c r="AR144">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS144">
         <v>309</v>
@@ -36150,7 +36150,7 @@
         </is>
       </c>
       <c r="D145">
-        <v>0.512</v>
+        <v>0.511946673397972</v>
       </c>
       <c r="E145">
         <v>144</v>
@@ -36264,7 +36264,7 @@
         <v>0.65</v>
       </c>
       <c r="AR145">
-        <v>0.54</v>
+        <v>0.5399897223436352</v>
       </c>
       <c r="AS145">
         <v>107</v>
@@ -36399,7 +36399,7 @@
         </is>
       </c>
       <c r="D146">
-        <v>0.512</v>
+        <v>0.511946673397972</v>
       </c>
       <c r="E146">
         <v>145</v>
@@ -36513,7 +36513,7 @@
         <v>0.65</v>
       </c>
       <c r="AR146">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS146">
         <v>76</v>
@@ -36648,7 +36648,7 @@
         </is>
       </c>
       <c r="D147">
-        <v>0.509</v>
+        <v>0.5092948387811768</v>
       </c>
       <c r="E147">
         <v>146</v>
@@ -36762,7 +36762,7 @@
         <v>0.5</v>
       </c>
       <c r="AR147">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS147">
         <v>141</v>
@@ -36897,7 +36897,7 @@
         </is>
       </c>
       <c r="D148">
-        <v>0.509</v>
+        <v>0.5092948387811768</v>
       </c>
       <c r="E148">
         <v>147</v>
@@ -37011,7 +37011,7 @@
         <v>0.5</v>
       </c>
       <c r="AR148">
-        <v>0.534</v>
+        <v>0.5341606724369765</v>
       </c>
       <c r="AS148">
         <v>118</v>
@@ -37146,7 +37146,7 @@
         </is>
       </c>
       <c r="D149">
-        <v>0.509</v>
+        <v>0.5092948387811768</v>
       </c>
       <c r="E149">
         <v>148</v>
@@ -37260,7 +37260,7 @@
         <v>0.5</v>
       </c>
       <c r="AR149">
-        <v>0.525</v>
+        <v>0.5254170975769883</v>
       </c>
       <c r="AS149">
         <v>128</v>
@@ -37395,7 +37395,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>0.509</v>
+        <v>0.5092948387811768</v>
       </c>
       <c r="E150">
         <v>149</v>
@@ -37509,7 +37509,7 @@
         <v>0.5</v>
       </c>
       <c r="AR150">
-        <v>0.5659999999999999</v>
+        <v>0.5662204469235997</v>
       </c>
       <c r="AS150">
         <v>86</v>
@@ -37644,7 +37644,7 @@
         </is>
       </c>
       <c r="D151">
-        <v>0.509</v>
+        <v>0.5092948387811768</v>
       </c>
       <c r="E151">
         <v>150</v>
@@ -37758,7 +37758,7 @@
         <v>0.5</v>
       </c>
       <c r="AR151">
-        <v>0.5659999999999999</v>
+        <v>0.5662204469235997</v>
       </c>
       <c r="AS151">
         <v>87</v>
@@ -37893,7 +37893,7 @@
         </is>
       </c>
       <c r="D152">
-        <v>0.509</v>
+        <v>0.5092948387811768</v>
       </c>
       <c r="E152">
         <v>151</v>
@@ -38007,7 +38007,7 @@
         <v>0.5</v>
       </c>
       <c r="AR152">
-        <v>0.488</v>
+        <v>0.4875282731837062</v>
       </c>
       <c r="AS152">
         <v>162</v>
@@ -38142,7 +38142,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>0.507</v>
+        <v>0.5066430041643816</v>
       </c>
       <c r="E153">
         <v>152</v>
@@ -38256,7 +38256,7 @@
         <v>0.35</v>
       </c>
       <c r="AR153">
-        <v>0.555</v>
+        <v>0.5545623471102822</v>
       </c>
       <c r="AS153">
         <v>97</v>
@@ -38391,7 +38391,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>0.504</v>
+        <v>0.5039911695475864</v>
       </c>
       <c r="E154">
         <v>153</v>
@@ -38505,7 +38505,7 @@
         <v>0.7</v>
       </c>
       <c r="AR154">
-        <v>0.499</v>
+        <v>0.4991863729970238</v>
       </c>
       <c r="AS154">
         <v>148</v>
@@ -38640,7 +38640,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>0.504</v>
+        <v>0.5039911695475864</v>
       </c>
       <c r="E155">
         <v>154</v>
@@ -38754,7 +38754,7 @@
         <v>0.7</v>
       </c>
       <c r="AR155">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS155">
         <v>311</v>
@@ -38889,7 +38889,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E156">
         <v>155</v>
@@ -39003,7 +39003,7 @@
         <v>0.55</v>
       </c>
       <c r="AR156">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS156">
         <v>124</v>
@@ -39138,7 +39138,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E157">
         <v>156</v>
@@ -39252,7 +39252,7 @@
         <v>0.55</v>
       </c>
       <c r="AR157">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS157">
         <v>66</v>
@@ -39387,7 +39387,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E158">
         <v>157</v>
@@ -39501,7 +39501,7 @@
         <v>0.55</v>
       </c>
       <c r="AR158">
-        <v>0.575</v>
+        <v>0.574964021783588</v>
       </c>
       <c r="AS158">
         <v>84</v>
@@ -39636,7 +39636,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E159">
         <v>158</v>
@@ -39750,7 +39750,7 @@
         <v>0.55</v>
       </c>
       <c r="AR159">
-        <v>0.397</v>
+        <v>0.397177999630495</v>
       </c>
       <c r="AS159">
         <v>294</v>
@@ -39885,7 +39885,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E160">
         <v>159</v>
@@ -39999,7 +39999,7 @@
         <v>0.55</v>
       </c>
       <c r="AR160">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS160">
         <v>216</v>
@@ -40134,7 +40134,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E161">
         <v>160</v>
@@ -40248,7 +40248,7 @@
         <v>0.55</v>
       </c>
       <c r="AR161">
-        <v>0.595</v>
+        <v>0.5953656964568936</v>
       </c>
       <c r="AS161">
         <v>63</v>
@@ -40383,7 +40383,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>0.501</v>
+        <v>0.5013393349307913</v>
       </c>
       <c r="E162">
         <v>161</v>
@@ -40497,7 +40497,7 @@
         <v>0.55</v>
       </c>
       <c r="AR162">
-        <v>0.549</v>
+        <v>0.5487332972036234</v>
       </c>
       <c r="AS162">
         <v>100</v>
@@ -40632,7 +40632,7 @@
         </is>
       </c>
       <c r="D163">
-        <v>0.496</v>
+        <v>0.4960356656972009</v>
       </c>
       <c r="E163">
         <v>162</v>
@@ -40746,7 +40746,7 @@
         <v>0.75</v>
       </c>
       <c r="AR163">
-        <v>0.461</v>
+        <v>0.4612975486037417</v>
       </c>
       <c r="AS163">
         <v>200</v>
@@ -40881,7 +40881,7 @@
         </is>
       </c>
       <c r="D164">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E164">
         <v>163</v>
@@ -40995,7 +40995,7 @@
         <v>0.6</v>
       </c>
       <c r="AR164">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS164">
         <v>252</v>
@@ -41130,7 +41130,7 @@
         </is>
       </c>
       <c r="D165">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E165">
         <v>164</v>
@@ -41244,7 +41244,7 @@
         <v>0.6</v>
       </c>
       <c r="AR165">
-        <v>0.49</v>
+        <v>0.4904427981370356</v>
       </c>
       <c r="AS165">
         <v>160</v>
@@ -41379,7 +41379,7 @@
         </is>
       </c>
       <c r="D166">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E166">
         <v>165</v>
@@ -41493,7 +41493,7 @@
         <v>0.6</v>
       </c>
       <c r="AR166">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS166">
         <v>117</v>
@@ -41628,7 +41628,7 @@
         </is>
       </c>
       <c r="D167">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E167">
         <v>166</v>
@@ -41742,7 +41742,7 @@
         <v>0.6</v>
       </c>
       <c r="AR167">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS167">
         <v>191</v>
@@ -41877,7 +41877,7 @@
         </is>
       </c>
       <c r="D168">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E168">
         <v>167</v>
@@ -41991,7 +41991,7 @@
         <v>0.6</v>
       </c>
       <c r="AR168">
-        <v>0.371</v>
+        <v>0.3709472750505305</v>
       </c>
       <c r="AS168">
         <v>320</v>
@@ -42126,7 +42126,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E169">
         <v>168</v>
@@ -42240,7 +42240,7 @@
         <v>0.6</v>
       </c>
       <c r="AR169">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS169">
         <v>281</v>
@@ -42375,7 +42375,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E170">
         <v>169</v>
@@ -42489,7 +42489,7 @@
         <v>0.6</v>
       </c>
       <c r="AR170">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS170">
         <v>121</v>
@@ -42624,7 +42624,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E171">
         <v>170</v>
@@ -42738,7 +42738,7 @@
         <v>0.6</v>
       </c>
       <c r="AR171">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS171">
         <v>123</v>
@@ -42873,7 +42873,7 @@
         </is>
       </c>
       <c r="D172">
-        <v>0.493</v>
+        <v>0.4933838310804057</v>
       </c>
       <c r="E172">
         <v>171</v>
@@ -42987,7 +42987,7 @@
         <v>0.6</v>
       </c>
       <c r="AR172">
-        <v>0.459</v>
+        <v>0.4593033999514636</v>
       </c>
       <c r="AS172">
         <v>202</v>
@@ -43119,7 +43119,7 @@
         </is>
       </c>
       <c r="D173">
-        <v>0.491</v>
+        <v>0.4907319964636106</v>
       </c>
       <c r="E173">
         <v>172</v>
@@ -43233,7 +43233,7 @@
         <v>0.45</v>
       </c>
       <c r="AR173">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS173">
         <v>112</v>
@@ -43368,7 +43368,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>0.485</v>
+        <v>0.4854283272300203</v>
       </c>
       <c r="E174">
         <v>173</v>
@@ -43482,7 +43482,7 @@
         <v>0.65</v>
       </c>
       <c r="AR174">
-        <v>0.461</v>
+        <v>0.4612975486037417</v>
       </c>
       <c r="AS174">
         <v>198</v>
@@ -43617,7 +43617,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>0.485</v>
+        <v>0.4854283272300203</v>
       </c>
       <c r="E175">
         <v>174</v>
@@ -43731,7 +43731,7 @@
         <v>0.65</v>
       </c>
       <c r="AR175">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS175">
         <v>184</v>
@@ -43866,7 +43866,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>0.483</v>
+        <v>0.4827764926132251</v>
       </c>
       <c r="E176">
         <v>175</v>
@@ -43980,7 +43980,7 @@
         <v>0.5</v>
       </c>
       <c r="AR176">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS176">
         <v>177</v>
@@ -44115,7 +44115,7 @@
         </is>
       </c>
       <c r="D177">
-        <v>0.483</v>
+        <v>0.4827764926132251</v>
       </c>
       <c r="E177">
         <v>176</v>
@@ -44229,7 +44229,7 @@
         <v>0.5</v>
       </c>
       <c r="AR177">
-        <v>0.488</v>
+        <v>0.4875282731837062</v>
       </c>
       <c r="AS177">
         <v>165</v>
@@ -44364,7 +44364,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>0.483</v>
+        <v>0.4827764926132251</v>
       </c>
       <c r="E178">
         <v>177</v>
@@ -44478,7 +44478,7 @@
         <v>0.5</v>
       </c>
       <c r="AR178">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS178">
         <v>254</v>
@@ -44613,7 +44613,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>0.483</v>
+        <v>0.4827764926132251</v>
       </c>
       <c r="E179">
         <v>178</v>
@@ -44727,7 +44727,7 @@
         <v>0.5</v>
       </c>
       <c r="AR179">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS179">
         <v>203</v>
@@ -44862,7 +44862,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>0.483</v>
+        <v>0.4827764926132251</v>
       </c>
       <c r="E180">
         <v>179</v>
@@ -44976,7 +44976,7 @@
         <v>0.5</v>
       </c>
       <c r="AR180">
-        <v>0.499</v>
+        <v>0.4991863729970238</v>
       </c>
       <c r="AS180">
         <v>150</v>
@@ -45111,7 +45111,7 @@
         </is>
       </c>
       <c r="D181">
-        <v>0.483</v>
+        <v>0.4827764926132251</v>
       </c>
       <c r="E181">
         <v>180</v>
@@ -45225,7 +45225,7 @@
         <v>0.5</v>
       </c>
       <c r="AR181">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS181">
         <v>239</v>
@@ -45360,7 +45360,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>0.48</v>
+        <v>0.4801246579964299</v>
       </c>
       <c r="E182">
         <v>181</v>
@@ -45474,7 +45474,7 @@
         <v>0.35</v>
       </c>
       <c r="AR182">
-        <v>0.514</v>
+        <v>0.5137589977636707</v>
       </c>
       <c r="AS182">
         <v>140</v>
@@ -45609,7 +45609,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>0.477</v>
+        <v>0.4774728233796347</v>
       </c>
       <c r="E183">
         <v>182</v>
@@ -45723,7 +45723,7 @@
         <v>0.7</v>
       </c>
       <c r="AR183">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS183">
         <v>220</v>
@@ -45858,7 +45858,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E184">
         <v>183</v>
@@ -45972,7 +45972,7 @@
         <v>0.55</v>
       </c>
       <c r="AR184">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS184">
         <v>209</v>
@@ -46107,7 +46107,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E185">
         <v>184</v>
@@ -46221,7 +46221,7 @@
         <v>0.55</v>
       </c>
       <c r="AR185">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS185">
         <v>260</v>
@@ -46356,7 +46356,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E186">
         <v>185</v>
@@ -46470,7 +46470,7 @@
         <v>0.55</v>
       </c>
       <c r="AR186">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS186">
         <v>176</v>
@@ -46605,7 +46605,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E187">
         <v>186</v>
@@ -46719,7 +46719,7 @@
         <v>0.55</v>
       </c>
       <c r="AR187">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS187">
         <v>127</v>
@@ -46854,7 +46854,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E188">
         <v>187</v>
@@ -46968,7 +46968,7 @@
         <v>0.55</v>
       </c>
       <c r="AR188">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS188">
         <v>81</v>
@@ -47103,7 +47103,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E189">
         <v>188</v>
@@ -47217,7 +47217,7 @@
         <v>0.55</v>
       </c>
       <c r="AR189">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS189">
         <v>242</v>
@@ -47352,7 +47352,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E190">
         <v>189</v>
@@ -47466,7 +47466,7 @@
         <v>0.55</v>
       </c>
       <c r="AR190">
-        <v>0.645</v>
+        <v>0.6449126206634933</v>
       </c>
       <c r="AS190">
         <v>34</v>
@@ -47601,7 +47601,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E191">
         <v>190</v>
@@ -47715,7 +47715,7 @@
         <v>0.55</v>
       </c>
       <c r="AR191">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS191">
         <v>172</v>
@@ -47850,7 +47850,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E192">
         <v>191</v>
@@ -47964,7 +47964,7 @@
         <v>0.55</v>
       </c>
       <c r="AR192">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS192">
         <v>75</v>
@@ -48099,7 +48099,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>0.475</v>
+        <v>0.4748209887628396</v>
       </c>
       <c r="E193">
         <v>192</v>
@@ -48213,7 +48213,7 @@
         <v>0.55</v>
       </c>
       <c r="AR193">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS193">
         <v>187</v>
@@ -48348,7 +48348,7 @@
         </is>
       </c>
       <c r="D194">
-        <v>0.472</v>
+        <v>0.4721691541460444</v>
       </c>
       <c r="E194">
         <v>193</v>
@@ -48462,7 +48462,7 @@
         <v>0.4</v>
       </c>
       <c r="AR194">
-        <v>0.5570000000000001</v>
+        <v>0.5574768720636116</v>
       </c>
       <c r="AS194">
         <v>93</v>
@@ -48597,7 +48597,7 @@
         </is>
       </c>
       <c r="D195">
-        <v>0.472</v>
+        <v>0.4721691541460444</v>
       </c>
       <c r="E195">
         <v>194</v>
@@ -48711,7 +48711,7 @@
         <v>0.4</v>
       </c>
       <c r="AR195">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS195">
         <v>120</v>
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="D196">
-        <v>0.472</v>
+        <v>0.4721691541460444</v>
       </c>
       <c r="E196">
         <v>195</v>
@@ -48960,7 +48960,7 @@
         <v>0.4</v>
       </c>
       <c r="AR196">
-        <v>0.607</v>
+        <v>0.6070237962702113</v>
       </c>
       <c r="AS196">
         <v>57</v>
@@ -49095,7 +49095,7 @@
         </is>
       </c>
       <c r="D197">
-        <v>0.472</v>
+        <v>0.4716108731740875</v>
       </c>
       <c r="E197">
         <v>196</v>
@@ -49206,7 +49206,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="AR197">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS197">
         <v>206</v>
@@ -49341,7 +49341,7 @@
         </is>
       </c>
       <c r="D198">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E198">
         <v>197</v>
@@ -49455,7 +49455,7 @@
         <v>0.6</v>
       </c>
       <c r="AR198">
-        <v>0.461</v>
+        <v>0.4612975486037417</v>
       </c>
       <c r="AS198">
         <v>199</v>
@@ -49590,7 +49590,7 @@
         </is>
       </c>
       <c r="D199">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E199">
         <v>198</v>
@@ -49704,7 +49704,7 @@
         <v>0.6</v>
       </c>
       <c r="AR199">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS199">
         <v>179</v>
@@ -49839,7 +49839,7 @@
         </is>
       </c>
       <c r="D200">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E200">
         <v>199</v>
@@ -49953,7 +49953,7 @@
         <v>0.6</v>
       </c>
       <c r="AR200">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS200">
         <v>265</v>
@@ -50088,7 +50088,7 @@
         </is>
       </c>
       <c r="D201">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E201">
         <v>200</v>
@@ -50202,7 +50202,7 @@
         <v>0.6</v>
       </c>
       <c r="AR201">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS201">
         <v>284</v>
@@ -50337,7 +50337,7 @@
         </is>
       </c>
       <c r="D202">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E202">
         <v>201</v>
@@ -50451,7 +50451,7 @@
         <v>0.6</v>
       </c>
       <c r="AR202">
-        <v>0.578</v>
+        <v>0.5778785467369174</v>
       </c>
       <c r="AS202">
         <v>77</v>
@@ -50586,7 +50586,7 @@
         </is>
       </c>
       <c r="D203">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E203">
         <v>202</v>
@@ -50700,7 +50700,7 @@
         <v>0.6</v>
       </c>
       <c r="AR203">
-        <v>0.49</v>
+        <v>0.4904427981370356</v>
       </c>
       <c r="AS203">
         <v>158</v>
@@ -50835,7 +50835,7 @@
         </is>
       </c>
       <c r="D204">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E204">
         <v>203</v>
@@ -50949,7 +50949,7 @@
         <v>0.6</v>
       </c>
       <c r="AR204">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS204">
         <v>221</v>
@@ -51084,7 +51084,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>0.467</v>
+        <v>0.4668654849124541</v>
       </c>
       <c r="E205">
         <v>204</v>
@@ -51198,7 +51198,7 @@
         <v>0.6</v>
       </c>
       <c r="AR205">
-        <v>0.459</v>
+        <v>0.4593033999514636</v>
       </c>
       <c r="AS205">
         <v>201</v>
@@ -51330,7 +51330,7 @@
         </is>
       </c>
       <c r="D206">
-        <v>0.464</v>
+        <v>0.4642136502956589</v>
       </c>
       <c r="E206">
         <v>205</v>
@@ -51444,7 +51444,7 @@
         <v>0.45</v>
       </c>
       <c r="AR206">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS206">
         <v>178</v>
@@ -51579,7 +51579,7 @@
         </is>
       </c>
       <c r="D207">
-        <v>0.464</v>
+        <v>0.4642136502956589</v>
       </c>
       <c r="E207">
         <v>206</v>
@@ -51693,7 +51693,7 @@
         <v>0.45</v>
       </c>
       <c r="AR207">
-        <v>0.339</v>
+        <v>0.3388875005639072</v>
       </c>
       <c r="AS207">
         <v>335</v>
@@ -51828,7 +51828,7 @@
         </is>
       </c>
       <c r="D208">
-        <v>0.464</v>
+        <v>0.4642136502956589</v>
       </c>
       <c r="E208">
         <v>207</v>
@@ -51942,7 +51942,7 @@
         <v>0.45</v>
       </c>
       <c r="AR208">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS208">
         <v>237</v>
@@ -52077,7 +52077,7 @@
         </is>
       </c>
       <c r="D209">
-        <v>0.459</v>
+        <v>0.4589099810620685</v>
       </c>
       <c r="E209">
         <v>208</v>
@@ -52191,7 +52191,7 @@
         <v>0.65</v>
       </c>
       <c r="AR209">
-        <v>0.482</v>
+        <v>0.4816992232770474</v>
       </c>
       <c r="AS209">
         <v>167</v>
@@ -52326,7 +52326,7 @@
         </is>
       </c>
       <c r="D210">
-        <v>0.459</v>
+        <v>0.4589099810620685</v>
       </c>
       <c r="E210">
         <v>209</v>
@@ -52440,7 +52440,7 @@
         <v>0.65</v>
       </c>
       <c r="AR210">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS210">
         <v>192</v>
@@ -52575,7 +52575,7 @@
         </is>
       </c>
       <c r="D211">
-        <v>0.459</v>
+        <v>0.4589099810620685</v>
       </c>
       <c r="E211">
         <v>210</v>
@@ -52689,7 +52689,7 @@
         <v>0.65</v>
       </c>
       <c r="AR211">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS211">
         <v>247</v>
@@ -52824,7 +52824,7 @@
         </is>
       </c>
       <c r="D212">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E212">
         <v>211</v>
@@ -52938,7 +52938,7 @@
         <v>0.5</v>
       </c>
       <c r="AR212">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS212">
         <v>240</v>
@@ -53073,7 +53073,7 @@
         </is>
       </c>
       <c r="D213">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E213">
         <v>212</v>
@@ -53187,7 +53187,7 @@
         <v>0.5</v>
       </c>
       <c r="AR213">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS213">
         <v>174</v>
@@ -53322,7 +53322,7 @@
         </is>
       </c>
       <c r="D214">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E214">
         <v>213</v>
@@ -53436,7 +53436,7 @@
         <v>0.5</v>
       </c>
       <c r="AR214">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS214">
         <v>126</v>
@@ -53571,7 +53571,7 @@
         </is>
       </c>
       <c r="D215">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E215">
         <v>214</v>
@@ -53685,7 +53685,7 @@
         <v>0.5</v>
       </c>
       <c r="AR215">
-        <v>0.5570000000000001</v>
+        <v>0.5574768720636116</v>
       </c>
       <c r="AS215">
         <v>95</v>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="D216">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E216">
         <v>215</v>
@@ -53934,7 +53934,7 @@
         <v>0.5</v>
       </c>
       <c r="AR216">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS216">
         <v>208</v>
@@ -54069,7 +54069,7 @@
         </is>
       </c>
       <c r="D217">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E217">
         <v>216</v>
@@ -54183,7 +54183,7 @@
         <v>0.5</v>
       </c>
       <c r="AR217">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS217">
         <v>304</v>
@@ -54318,7 +54318,7 @@
         </is>
       </c>
       <c r="D218">
-        <v>0.456</v>
+        <v>0.4562581464452734</v>
       </c>
       <c r="E218">
         <v>217</v>
@@ -54432,7 +54432,7 @@
         <v>0.5</v>
       </c>
       <c r="AR218">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS218">
         <v>145</v>
@@ -54567,7 +54567,7 @@
         </is>
       </c>
       <c r="D219">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E219">
         <v>218</v>
@@ -54681,7 +54681,7 @@
         <v>0.55</v>
       </c>
       <c r="AR219">
-        <v>0.409</v>
+        <v>0.4088360994438126</v>
       </c>
       <c r="AS219">
         <v>276</v>
@@ -54816,7 +54816,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E220">
         <v>219</v>
@@ -54930,7 +54930,7 @@
         <v>0.55</v>
       </c>
       <c r="AR220">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS220">
         <v>307</v>
@@ -55065,7 +55065,7 @@
         </is>
       </c>
       <c r="D221">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E221">
         <v>220</v>
@@ -55179,7 +55179,7 @@
         <v>0.55</v>
       </c>
       <c r="AR221">
-        <v>0.499</v>
+        <v>0.4991863729970238</v>
       </c>
       <c r="AS221">
         <v>153</v>
@@ -55314,7 +55314,7 @@
         </is>
       </c>
       <c r="D222">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E222">
         <v>221</v>
@@ -55428,7 +55428,7 @@
         <v>0.55</v>
       </c>
       <c r="AR222">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS222">
         <v>217</v>
@@ -55563,7 +55563,7 @@
         </is>
       </c>
       <c r="D223">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E223">
         <v>222</v>
@@ -55677,7 +55677,7 @@
         <v>0.55</v>
       </c>
       <c r="AR223">
-        <v>0.481</v>
+        <v>0.480778846975996</v>
       </c>
       <c r="AS223">
         <v>168</v>
@@ -55809,7 +55809,7 @@
         </is>
       </c>
       <c r="D224">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E224">
         <v>223</v>
@@ -55923,7 +55923,7 @@
         <v>0.55</v>
       </c>
       <c r="AR224">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS224">
         <v>219</v>
@@ -56058,7 +56058,7 @@
         </is>
       </c>
       <c r="D225">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E225">
         <v>224</v>
@@ -56172,7 +56172,7 @@
         <v>0.55</v>
       </c>
       <c r="AR225">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS225">
         <v>287</v>
@@ -56307,7 +56307,7 @@
         </is>
       </c>
       <c r="D226">
-        <v>0.448</v>
+        <v>0.4483026425948879</v>
       </c>
       <c r="E226">
         <v>225</v>
@@ -56421,7 +56421,7 @@
         <v>0.55</v>
       </c>
       <c r="AR226">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS226">
         <v>249</v>
@@ -56556,7 +56556,7 @@
         </is>
       </c>
       <c r="D227">
-        <v>0.446</v>
+        <v>0.4456508079780928</v>
       </c>
       <c r="E227">
         <v>226</v>
@@ -56670,7 +56670,7 @@
         <v>0.4</v>
       </c>
       <c r="AR227">
-        <v>0.418</v>
+        <v>0.4175796743038008</v>
       </c>
       <c r="AS227">
         <v>270</v>
@@ -56805,7 +56805,7 @@
         </is>
       </c>
       <c r="D228">
-        <v>0.446</v>
+        <v>0.4456508079780928</v>
       </c>
       <c r="E228">
         <v>227</v>
@@ -56919,7 +56919,7 @@
         <v>0.4</v>
       </c>
       <c r="AR228">
-        <v>0.397</v>
+        <v>0.397177999630495</v>
       </c>
       <c r="AS228">
         <v>297</v>
@@ -57054,7 +57054,7 @@
         </is>
       </c>
       <c r="D229">
-        <v>0.446</v>
+        <v>0.4456508079780928</v>
       </c>
       <c r="E229">
         <v>228</v>
@@ -57168,7 +57168,7 @@
         <v>0.4</v>
       </c>
       <c r="AR229">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS229">
         <v>234</v>
@@ -57303,7 +57303,7 @@
         </is>
       </c>
       <c r="D230">
-        <v>0.446</v>
+        <v>0.4456508079780928</v>
       </c>
       <c r="E230">
         <v>229</v>
@@ -57417,7 +57417,7 @@
         <v>0.4</v>
       </c>
       <c r="AR230">
-        <v>0.488</v>
+        <v>0.4875282731837062</v>
       </c>
       <c r="AS230">
         <v>161</v>
@@ -57552,7 +57552,7 @@
         </is>
       </c>
       <c r="D231">
-        <v>0.44</v>
+        <v>0.4403471387445024</v>
       </c>
       <c r="E231">
         <v>230</v>
@@ -57666,7 +57666,7 @@
         <v>0.6</v>
       </c>
       <c r="AR231">
-        <v>0.441</v>
+        <v>0.4408958739304359</v>
       </c>
       <c r="AS231">
         <v>224</v>
@@ -57801,7 +57801,7 @@
         </is>
       </c>
       <c r="D232">
-        <v>0.44</v>
+        <v>0.4403471387445024</v>
       </c>
       <c r="E232">
         <v>231</v>
@@ -57915,7 +57915,7 @@
         <v>0.6</v>
       </c>
       <c r="AR232">
-        <v>0.409</v>
+        <v>0.4088360994438126</v>
       </c>
       <c r="AS232">
         <v>273</v>
@@ -58050,7 +58050,7 @@
         </is>
       </c>
       <c r="D233">
-        <v>0.44</v>
+        <v>0.4403471387445024</v>
       </c>
       <c r="E233">
         <v>232</v>
@@ -58164,7 +58164,7 @@
         <v>0.6</v>
       </c>
       <c r="AR233">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS233">
         <v>285</v>
@@ -58299,7 +58299,7 @@
         </is>
       </c>
       <c r="D234">
-        <v>0.44</v>
+        <v>0.4403471387445024</v>
       </c>
       <c r="E234">
         <v>233</v>
@@ -58413,7 +58413,7 @@
         <v>0.6</v>
       </c>
       <c r="AR234">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS234">
         <v>257</v>
@@ -58548,7 +58548,7 @@
         </is>
       </c>
       <c r="D235">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E235">
         <v>234</v>
@@ -58662,7 +58662,7 @@
         <v>0.45</v>
       </c>
       <c r="AR235">
-        <v>0.409</v>
+        <v>0.4088360994438126</v>
       </c>
       <c r="AS235">
         <v>275</v>
@@ -58797,7 +58797,7 @@
         </is>
       </c>
       <c r="D236">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E236">
         <v>235</v>
@@ -58911,7 +58911,7 @@
         <v>0.45</v>
       </c>
       <c r="AR236">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS236">
         <v>305</v>
@@ -59046,7 +59046,7 @@
         </is>
       </c>
       <c r="D237">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E237">
         <v>236</v>
@@ -59160,7 +59160,7 @@
         <v>0.45</v>
       </c>
       <c r="AR237">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS237">
         <v>250</v>
@@ -59295,7 +59295,7 @@
         </is>
       </c>
       <c r="D238">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E238">
         <v>237</v>
@@ -59409,7 +59409,7 @@
         <v>0.45</v>
       </c>
       <c r="AR238">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS238">
         <v>175</v>
@@ -59544,7 +59544,7 @@
         </is>
       </c>
       <c r="D239">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E239">
         <v>238</v>
@@ -59658,7 +59658,7 @@
         <v>0.45</v>
       </c>
       <c r="AR239">
-        <v>0.467</v>
+        <v>0.4671265985104004</v>
       </c>
       <c r="AS239">
         <v>196</v>
@@ -59793,7 +59793,7 @@
         </is>
       </c>
       <c r="D240">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E240">
         <v>239</v>
@@ -59907,7 +59907,7 @@
         <v>0.45</v>
       </c>
       <c r="AR240">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS240">
         <v>241</v>
@@ -60042,7 +60042,7 @@
         </is>
       </c>
       <c r="D241">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E241">
         <v>240</v>
@@ -60156,7 +60156,7 @@
         <v>0.45</v>
       </c>
       <c r="AR241">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS241">
         <v>267</v>
@@ -60291,7 +60291,7 @@
         </is>
       </c>
       <c r="D242">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E242">
         <v>241</v>
@@ -60405,7 +60405,7 @@
         <v>0.45</v>
       </c>
       <c r="AR242">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS242">
         <v>236</v>
@@ -60540,7 +60540,7 @@
         </is>
       </c>
       <c r="D243">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E243">
         <v>242</v>
@@ -60654,7 +60654,7 @@
         <v>0.45</v>
       </c>
       <c r="AR243">
-        <v>0.496</v>
+        <v>0.4962718480436943</v>
       </c>
       <c r="AS243">
         <v>154</v>
@@ -60789,7 +60789,7 @@
         </is>
       </c>
       <c r="D244">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E244">
         <v>243</v>
@@ -60903,7 +60903,7 @@
         <v>0.45</v>
       </c>
       <c r="AR244">
-        <v>0.537</v>
+        <v>0.5370751973903058</v>
       </c>
       <c r="AS244">
         <v>111</v>
@@ -61038,7 +61038,7 @@
         </is>
       </c>
       <c r="D245">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E245">
         <v>244</v>
@@ -61152,7 +61152,7 @@
         <v>0.45</v>
       </c>
       <c r="AR245">
-        <v>0.598</v>
+        <v>0.5982802214102231</v>
       </c>
       <c r="AS245">
         <v>59</v>
@@ -61287,7 +61287,7 @@
         </is>
       </c>
       <c r="D246">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E246">
         <v>245</v>
@@ -61401,7 +61401,7 @@
         <v>0.45</v>
       </c>
       <c r="AR246">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS246">
         <v>238</v>
@@ -61536,7 +61536,7 @@
         </is>
       </c>
       <c r="D247">
-        <v>0.438</v>
+        <v>0.4376953041277072</v>
       </c>
       <c r="E247">
         <v>246</v>
@@ -61650,7 +61650,7 @@
         <v>0.45</v>
       </c>
       <c r="AR247">
-        <v>0.368</v>
+        <v>0.3680327500972012</v>
       </c>
       <c r="AS247">
         <v>325</v>
@@ -61785,7 +61785,7 @@
         </is>
       </c>
       <c r="D248">
-        <v>0.435</v>
+        <v>0.4350434695109121</v>
       </c>
       <c r="E248">
         <v>247</v>
@@ -61899,7 +61899,7 @@
         <v>0.3</v>
       </c>
       <c r="AR248">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS248">
         <v>169</v>
@@ -62034,7 +62034,7 @@
         </is>
       </c>
       <c r="D249">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E249">
         <v>248</v>
@@ -62148,7 +62148,7 @@
         <v>0.5</v>
       </c>
       <c r="AR249">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS249">
         <v>188</v>
@@ -62283,7 +62283,7 @@
         </is>
       </c>
       <c r="D250">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E250">
         <v>249</v>
@@ -62397,7 +62397,7 @@
         <v>0.5</v>
       </c>
       <c r="AR250">
-        <v>0.441</v>
+        <v>0.4408958739304359</v>
       </c>
       <c r="AS250">
         <v>229</v>
@@ -62532,7 +62532,7 @@
         </is>
       </c>
       <c r="D251">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E251">
         <v>250</v>
@@ -62646,7 +62646,7 @@
         <v>0.5</v>
       </c>
       <c r="AR251">
-        <v>0.467</v>
+        <v>0.4671265985104004</v>
       </c>
       <c r="AS251">
         <v>193</v>
@@ -62781,7 +62781,7 @@
         </is>
       </c>
       <c r="D252">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E252">
         <v>251</v>
@@ -62895,7 +62895,7 @@
         <v>0.5</v>
       </c>
       <c r="AR252">
-        <v>0.339</v>
+        <v>0.3388875005639072</v>
       </c>
       <c r="AS252">
         <v>334</v>
@@ -63030,7 +63030,7 @@
         </is>
       </c>
       <c r="D253">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E253">
         <v>252</v>
@@ -63144,7 +63144,7 @@
         <v>0.5</v>
       </c>
       <c r="AR253">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS253">
         <v>244</v>
@@ -63279,7 +63279,7 @@
         </is>
       </c>
       <c r="D254">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E254">
         <v>253</v>
@@ -63393,7 +63393,7 @@
         <v>0.5</v>
       </c>
       <c r="AR254">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS254">
         <v>302</v>
@@ -63528,7 +63528,7 @@
         </is>
       </c>
       <c r="D255">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E255">
         <v>254</v>
@@ -63642,7 +63642,7 @@
         <v>0.5</v>
       </c>
       <c r="AR255">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS255">
         <v>329</v>
@@ -63777,7 +63777,7 @@
         </is>
       </c>
       <c r="D256">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E256">
         <v>255</v>
@@ -63891,7 +63891,7 @@
         <v>0.5</v>
       </c>
       <c r="AR256">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS256">
         <v>283</v>
@@ -64026,7 +64026,7 @@
         </is>
       </c>
       <c r="D257">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E257">
         <v>256</v>
@@ -64140,7 +64140,7 @@
         <v>0.5</v>
       </c>
       <c r="AR257">
-        <v>0.575</v>
+        <v>0.574964021783588</v>
       </c>
       <c r="AS257">
         <v>82</v>
@@ -64275,7 +64275,7 @@
         </is>
       </c>
       <c r="D258">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E258">
         <v>257</v>
@@ -64389,7 +64389,7 @@
         <v>0.5</v>
       </c>
       <c r="AR258">
-        <v>0.416</v>
+        <v>0.4163525059023989</v>
       </c>
       <c r="AS258">
         <v>271</v>
@@ -64521,7 +64521,7 @@
         </is>
       </c>
       <c r="D259">
-        <v>0.43</v>
+        <v>0.4297398002773217</v>
       </c>
       <c r="E259">
         <v>258</v>
@@ -64635,7 +64635,7 @@
         <v>0.5</v>
       </c>
       <c r="AR259">
-        <v>0.409</v>
+        <v>0.4088360994438126</v>
       </c>
       <c r="AS259">
         <v>274</v>
@@ -64770,7 +64770,7 @@
         </is>
       </c>
       <c r="D260">
-        <v>0.427</v>
+        <v>0.4270879656605265</v>
       </c>
       <c r="E260">
         <v>259</v>
@@ -64884,7 +64884,7 @@
         <v>0.35</v>
       </c>
       <c r="AR260">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS260">
         <v>248</v>
@@ -65019,7 +65019,7 @@
         </is>
       </c>
       <c r="D261">
-        <v>0.427</v>
+        <v>0.4270879656605265</v>
       </c>
       <c r="E261">
         <v>260</v>
@@ -65133,7 +65133,7 @@
         <v>0.35</v>
       </c>
       <c r="AR261">
-        <v>0.488</v>
+        <v>0.4875282731837062</v>
       </c>
       <c r="AS261">
         <v>163</v>
@@ -65268,7 +65268,7 @@
         </is>
       </c>
       <c r="D262">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E262">
         <v>261</v>
@@ -65382,7 +65382,7 @@
         <v>0.55</v>
       </c>
       <c r="AR262">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS262">
         <v>259</v>
@@ -65517,7 +65517,7 @@
         </is>
       </c>
       <c r="D263">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E263">
         <v>262</v>
@@ -65631,7 +65631,7 @@
         <v>0.55</v>
       </c>
       <c r="AR263">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS263">
         <v>264</v>
@@ -65766,7 +65766,7 @@
         </is>
       </c>
       <c r="D264">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E264">
         <v>263</v>
@@ -65880,7 +65880,7 @@
         <v>0.55</v>
       </c>
       <c r="AR264">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS264">
         <v>293</v>
@@ -66015,7 +66015,7 @@
         </is>
       </c>
       <c r="D265">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E265">
         <v>264</v>
@@ -66129,7 +66129,7 @@
         <v>0.55</v>
       </c>
       <c r="AR265">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS265">
         <v>185</v>
@@ -66264,7 +66264,7 @@
         </is>
       </c>
       <c r="D266">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E266">
         <v>265</v>
@@ -66378,7 +66378,7 @@
         <v>0.55</v>
       </c>
       <c r="AR266">
-        <v>0.318</v>
+        <v>0.3184858258906015</v>
       </c>
       <c r="AS266">
         <v>341</v>
@@ -66513,7 +66513,7 @@
         </is>
       </c>
       <c r="D267">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E267">
         <v>266</v>
@@ -66627,7 +66627,7 @@
         <v>0.55</v>
       </c>
       <c r="AR267">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS267">
         <v>186</v>
@@ -66762,7 +66762,7 @@
         </is>
       </c>
       <c r="D268">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E268">
         <v>267</v>
@@ -66876,7 +66876,7 @@
         <v>0.55</v>
       </c>
       <c r="AR268">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS268">
         <v>330</v>
@@ -67011,7 +67011,7 @@
         </is>
       </c>
       <c r="D269">
-        <v>0.422</v>
+        <v>0.4217842964269362</v>
       </c>
       <c r="E269">
         <v>268</v>
@@ -67125,7 +67125,7 @@
         <v>0.55</v>
       </c>
       <c r="AR269">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS269">
         <v>331</v>
@@ -67260,7 +67260,7 @@
         </is>
       </c>
       <c r="D270">
-        <v>0.419</v>
+        <v>0.4191324618101411</v>
       </c>
       <c r="E270">
         <v>269</v>
@@ -67374,7 +67374,7 @@
         <v>0.4</v>
       </c>
       <c r="AR270">
-        <v>0.528</v>
+        <v>0.5283316225303176</v>
       </c>
       <c r="AS270">
         <v>125</v>
@@ -67509,7 +67509,7 @@
         </is>
       </c>
       <c r="D271">
-        <v>0.419</v>
+        <v>0.4191324618101411</v>
       </c>
       <c r="E271">
         <v>270</v>
@@ -67623,7 +67623,7 @@
         <v>0.4</v>
       </c>
       <c r="AR271">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS271">
         <v>300</v>
@@ -67758,7 +67758,7 @@
         </is>
       </c>
       <c r="D272">
-        <v>0.419</v>
+        <v>0.4191324618101411</v>
       </c>
       <c r="E272">
         <v>271</v>
@@ -67872,7 +67872,7 @@
         <v>0.4</v>
       </c>
       <c r="AR272">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS272">
         <v>243</v>
@@ -68007,7 +68007,7 @@
         </is>
       </c>
       <c r="D273">
-        <v>0.419</v>
+        <v>0.4191324618101411</v>
       </c>
       <c r="E273">
         <v>272</v>
@@ -68121,7 +68121,7 @@
         <v>0.4</v>
       </c>
       <c r="AR273">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS273">
         <v>173</v>
@@ -68256,7 +68256,7 @@
         </is>
       </c>
       <c r="D274">
-        <v>0.414</v>
+        <v>0.4138287925765507</v>
       </c>
       <c r="E274">
         <v>273</v>
@@ -68370,7 +68370,7 @@
         <v>0.6</v>
       </c>
       <c r="AR274">
-        <v>0.482</v>
+        <v>0.4816992232770474</v>
       </c>
       <c r="AS274">
         <v>166</v>
@@ -68505,7 +68505,7 @@
         </is>
       </c>
       <c r="D275">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E275">
         <v>274</v>
@@ -68619,7 +68619,7 @@
         <v>0.45</v>
       </c>
       <c r="AR275">
-        <v>0.397</v>
+        <v>0.397177999630495</v>
       </c>
       <c r="AS275">
         <v>296</v>
@@ -68754,7 +68754,7 @@
         </is>
       </c>
       <c r="D276">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E276">
         <v>275</v>
@@ -68868,7 +68868,7 @@
         <v>0.45</v>
       </c>
       <c r="AR276">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS276">
         <v>292</v>
@@ -69003,7 +69003,7 @@
         </is>
       </c>
       <c r="D277">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E277">
         <v>276</v>
@@ -69117,7 +69117,7 @@
         <v>0.45</v>
       </c>
       <c r="AR277">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS277">
         <v>253</v>
@@ -69252,7 +69252,7 @@
         </is>
       </c>
       <c r="D278">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E278">
         <v>277</v>
@@ -69366,7 +69366,7 @@
         <v>0.45</v>
       </c>
       <c r="AR278">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS278">
         <v>212</v>
@@ -69501,7 +69501,7 @@
         </is>
       </c>
       <c r="D279">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E279">
         <v>278</v>
@@ -69615,7 +69615,7 @@
         <v>0.45</v>
       </c>
       <c r="AR279">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS279">
         <v>319</v>
@@ -69750,7 +69750,7 @@
         </is>
       </c>
       <c r="D280">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E280">
         <v>279</v>
@@ -69864,7 +69864,7 @@
         <v>0.45</v>
       </c>
       <c r="AR280">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS280">
         <v>255</v>
@@ -69999,7 +69999,7 @@
         </is>
       </c>
       <c r="D281">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E281">
         <v>280</v>
@@ -70113,7 +70113,7 @@
         <v>0.45</v>
       </c>
       <c r="AR281">
-        <v>0.33</v>
+        <v>0.330143925703919</v>
       </c>
       <c r="AS281">
         <v>339</v>
@@ -70248,7 +70248,7 @@
         </is>
       </c>
       <c r="D282">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E282">
         <v>281</v>
@@ -70362,7 +70362,7 @@
         <v>0.45</v>
       </c>
       <c r="AR282">
-        <v>0.549</v>
+        <v>0.5487332972036234</v>
       </c>
       <c r="AS282">
         <v>99</v>
@@ -70497,7 +70497,7 @@
         </is>
       </c>
       <c r="D283">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E283">
         <v>282</v>
@@ -70611,7 +70611,7 @@
         <v>0.45</v>
       </c>
       <c r="AR283">
-        <v>0.49</v>
+        <v>0.4904427981370356</v>
       </c>
       <c r="AS283">
         <v>157</v>
@@ -70746,7 +70746,7 @@
         </is>
       </c>
       <c r="D284">
-        <v>0.411</v>
+        <v>0.4111769579597556</v>
       </c>
       <c r="E284">
         <v>283</v>
@@ -70860,7 +70860,7 @@
         <v>0.45</v>
       </c>
       <c r="AR284">
-        <v>0.45</v>
+        <v>0.4496394487904241</v>
       </c>
       <c r="AS284">
         <v>218</v>
@@ -70995,7 +70995,7 @@
         </is>
       </c>
       <c r="D285">
-        <v>0.409</v>
+        <v>0.4085251233429604</v>
       </c>
       <c r="E285">
         <v>284</v>
@@ -71109,7 +71109,7 @@
         <v>0.3</v>
       </c>
       <c r="AR285">
-        <v>0.476</v>
+        <v>0.4758701733703886</v>
       </c>
       <c r="AS285">
         <v>181</v>
@@ -71244,7 +71244,7 @@
         </is>
       </c>
       <c r="D286">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E286">
         <v>285</v>
@@ -71358,7 +71358,7 @@
         <v>0.5</v>
       </c>
       <c r="AR286">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS286">
         <v>289</v>
@@ -71493,7 +71493,7 @@
         </is>
       </c>
       <c r="D287">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E287">
         <v>286</v>
@@ -71607,7 +71607,7 @@
         <v>0.5</v>
       </c>
       <c r="AR287">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS287">
         <v>290</v>
@@ -71742,7 +71742,7 @@
         </is>
       </c>
       <c r="D288">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E288">
         <v>287</v>
@@ -71856,7 +71856,7 @@
         <v>0.5</v>
       </c>
       <c r="AR288">
-        <v>0.47</v>
+        <v>0.4700411234637298</v>
       </c>
       <c r="AS288">
         <v>189</v>
@@ -71991,7 +71991,7 @@
         </is>
       </c>
       <c r="D289">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E289">
         <v>288</v>
@@ -72105,7 +72105,7 @@
         <v>0.5</v>
       </c>
       <c r="AR289">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS289">
         <v>291</v>
@@ -72240,7 +72240,7 @@
         </is>
       </c>
       <c r="D290">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E290">
         <v>289</v>
@@ -72354,7 +72354,7 @@
         <v>0.5</v>
       </c>
       <c r="AR290">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS290">
         <v>278</v>
@@ -72489,7 +72489,7 @@
         </is>
       </c>
       <c r="D291">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E291">
         <v>290</v>
@@ -72603,7 +72603,7 @@
         <v>0.5</v>
       </c>
       <c r="AR291">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS291">
         <v>246</v>
@@ -72738,7 +72738,7 @@
         </is>
       </c>
       <c r="D292">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E292">
         <v>291</v>
@@ -72852,7 +72852,7 @@
         <v>0.5</v>
       </c>
       <c r="AR292">
-        <v>0.441</v>
+        <v>0.4408958739304359</v>
       </c>
       <c r="AS292">
         <v>225</v>
@@ -72987,7 +72987,7 @@
         </is>
       </c>
       <c r="D293">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E293">
         <v>292</v>
@@ -73101,7 +73101,7 @@
         <v>0.5</v>
       </c>
       <c r="AR293">
-        <v>0.52</v>
+        <v>0.5195880476703295</v>
       </c>
       <c r="AS293">
         <v>133</v>
@@ -73236,7 +73236,7 @@
         </is>
       </c>
       <c r="D294">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E294">
         <v>293</v>
@@ -73350,7 +73350,7 @@
         <v>0.5</v>
       </c>
       <c r="AR294">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS294">
         <v>312</v>
@@ -73485,7 +73485,7 @@
         </is>
       </c>
       <c r="D295">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E295">
         <v>294</v>
@@ -73599,7 +73599,7 @@
         <v>0.5</v>
       </c>
       <c r="AR295">
-        <v>0.371</v>
+        <v>0.3709472750505305</v>
       </c>
       <c r="AS295">
         <v>321</v>
@@ -73734,7 +73734,7 @@
         </is>
       </c>
       <c r="D296">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E296">
         <v>295</v>
@@ -73848,7 +73848,7 @@
         <v>0.5</v>
       </c>
       <c r="AR296">
-        <v>0.441</v>
+        <v>0.4408958739304359</v>
       </c>
       <c r="AS296">
         <v>227</v>
@@ -73983,7 +73983,7 @@
         </is>
       </c>
       <c r="D297">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E297">
         <v>296</v>
@@ -74097,7 +74097,7 @@
         <v>0.5</v>
       </c>
       <c r="AR297">
-        <v>0.339</v>
+        <v>0.3388875005639072</v>
       </c>
       <c r="AS297">
         <v>336</v>
@@ -74232,7 +74232,7 @@
         </is>
       </c>
       <c r="D298">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E298">
         <v>297</v>
@@ -74346,7 +74346,7 @@
         <v>0.5</v>
       </c>
       <c r="AR298">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS298">
         <v>315</v>
@@ -74481,7 +74481,7 @@
         </is>
       </c>
       <c r="D299">
-        <v>0.403</v>
+        <v>0.40322145410937</v>
       </c>
       <c r="E299">
         <v>298</v>
@@ -74595,7 +74595,7 @@
         <v>0.5</v>
       </c>
       <c r="AR299">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS299">
         <v>258</v>
@@ -74730,7 +74730,7 @@
         </is>
       </c>
       <c r="D300">
-        <v>0.395</v>
+        <v>0.3952659502589846</v>
       </c>
       <c r="E300">
         <v>299</v>
@@ -74844,7 +74844,7 @@
         <v>0.55</v>
       </c>
       <c r="AR300">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS300">
         <v>282</v>
@@ -74979,7 +74979,7 @@
         </is>
       </c>
       <c r="D301">
-        <v>0.393</v>
+        <v>0.3934515371001247</v>
       </c>
       <c r="E301">
         <v>300</v>
@@ -75090,7 +75090,7 @@
         <v>0.4736842105263158</v>
       </c>
       <c r="AR301">
-        <v>0.339</v>
+        <v>0.3388875005639072</v>
       </c>
       <c r="AS301">
         <v>333</v>
@@ -75225,7 +75225,7 @@
         </is>
       </c>
       <c r="D302">
-        <v>0.393</v>
+        <v>0.3926141156421894</v>
       </c>
       <c r="E302">
         <v>301</v>
@@ -75339,7 +75339,7 @@
         <v>0.4</v>
       </c>
       <c r="AR302">
-        <v>0.54</v>
+        <v>0.5399897223436352</v>
       </c>
       <c r="AS302">
         <v>108</v>
@@ -75474,7 +75474,7 @@
         </is>
       </c>
       <c r="D303">
-        <v>0.393</v>
+        <v>0.3926141156421894</v>
       </c>
       <c r="E303">
         <v>302</v>
@@ -75588,7 +75588,7 @@
         <v>0.4</v>
       </c>
       <c r="AR303">
-        <v>0.458</v>
+        <v>0.4583830236504123</v>
       </c>
       <c r="AS303">
         <v>211</v>
@@ -75723,7 +75723,7 @@
         </is>
       </c>
       <c r="D304">
-        <v>0.393</v>
+        <v>0.3926141156421894</v>
       </c>
       <c r="E304">
         <v>303</v>
@@ -75837,7 +75837,7 @@
         <v>0.4</v>
       </c>
       <c r="AR304">
-        <v>0.508</v>
+        <v>0.507929947857012</v>
       </c>
       <c r="AS304">
         <v>142</v>
@@ -75972,7 +75972,7 @@
         </is>
       </c>
       <c r="D305">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E305">
         <v>304</v>
@@ -76086,7 +76086,7 @@
         <v>0.45</v>
       </c>
       <c r="AR305">
-        <v>0.339</v>
+        <v>0.3388875005639072</v>
       </c>
       <c r="AS305">
         <v>337</v>
@@ -76221,7 +76221,7 @@
         </is>
       </c>
       <c r="D306">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E306">
         <v>305</v>
@@ -76335,7 +76335,7 @@
         <v>0.45</v>
       </c>
       <c r="AR306">
-        <v>0.441</v>
+        <v>0.4408958739304359</v>
       </c>
       <c r="AS306">
         <v>228</v>
@@ -76470,7 +76470,7 @@
         </is>
       </c>
       <c r="D307">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E307">
         <v>306</v>
@@ -76584,7 +76584,7 @@
         <v>0.45</v>
       </c>
       <c r="AR307">
-        <v>0.409</v>
+        <v>0.4088360994438126</v>
       </c>
       <c r="AS307">
         <v>277</v>
@@ -76719,7 +76719,7 @@
         </is>
       </c>
       <c r="D308">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E308">
         <v>307</v>
@@ -76833,7 +76833,7 @@
         <v>0.45</v>
       </c>
       <c r="AR308">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS308">
         <v>327</v>
@@ -76968,7 +76968,7 @@
         </is>
       </c>
       <c r="D309">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E309">
         <v>308</v>
@@ -77082,7 +77082,7 @@
         <v>0.45</v>
       </c>
       <c r="AR309">
-        <v>0.479</v>
+        <v>0.478784698323718</v>
       </c>
       <c r="AS309">
         <v>171</v>
@@ -77217,7 +77217,7 @@
         </is>
       </c>
       <c r="D310">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E310">
         <v>309</v>
@@ -77331,7 +77331,7 @@
         <v>0.45</v>
       </c>
       <c r="AR310">
-        <v>0.441</v>
+        <v>0.4408958739304359</v>
       </c>
       <c r="AS310">
         <v>226</v>
@@ -77466,7 +77466,7 @@
         </is>
       </c>
       <c r="D311">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E311">
         <v>310</v>
@@ -77580,7 +77580,7 @@
         <v>0.45</v>
       </c>
       <c r="AR311">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS311">
         <v>314</v>
@@ -77715,7 +77715,7 @@
         </is>
       </c>
       <c r="D312">
-        <v>0.385</v>
+        <v>0.3846586117918039</v>
       </c>
       <c r="E312">
         <v>311</v>
@@ -77829,7 +77829,7 @@
         <v>0.45</v>
       </c>
       <c r="AR312">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS312">
         <v>286</v>
@@ -77964,7 +77964,7 @@
         </is>
       </c>
       <c r="D313">
-        <v>0.382</v>
+        <v>0.3820067771750087</v>
       </c>
       <c r="E313">
         <v>312</v>
@@ -78078,7 +78078,7 @@
         <v>0.3</v>
       </c>
       <c r="AR313">
-        <v>0.397</v>
+        <v>0.397177999630495</v>
       </c>
       <c r="AS313">
         <v>298</v>
@@ -78213,7 +78213,7 @@
         </is>
       </c>
       <c r="D314">
-        <v>0.382</v>
+        <v>0.3820067771750087</v>
       </c>
       <c r="E314">
         <v>313</v>
@@ -78327,7 +78327,7 @@
         <v>0.3</v>
       </c>
       <c r="AR314">
-        <v>0.397</v>
+        <v>0.397177999630495</v>
       </c>
       <c r="AS314">
         <v>295</v>
@@ -78462,7 +78462,7 @@
         </is>
       </c>
       <c r="D315">
-        <v>0.374</v>
+        <v>0.3740512733246232</v>
       </c>
       <c r="E315">
         <v>314</v>
@@ -78576,7 +78576,7 @@
         <v>0.35</v>
       </c>
       <c r="AR315">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS315">
         <v>306</v>
@@ -78711,7 +78711,7 @@
         </is>
       </c>
       <c r="D316">
-        <v>0.374</v>
+        <v>0.3740512733246232</v>
       </c>
       <c r="E316">
         <v>315</v>
@@ -78825,7 +78825,7 @@
         <v>0.35</v>
       </c>
       <c r="AR316">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS316">
         <v>262</v>
@@ -78960,7 +78960,7 @@
         </is>
       </c>
       <c r="D317">
-        <v>0.374</v>
+        <v>0.3740512733246232</v>
       </c>
       <c r="E317">
         <v>316</v>
@@ -79074,7 +79074,7 @@
         <v>0.35</v>
       </c>
       <c r="AR317">
-        <v>0.412</v>
+        <v>0.411750624397142</v>
       </c>
       <c r="AS317">
         <v>272</v>
@@ -79209,7 +79209,7 @@
         </is>
       </c>
       <c r="D318">
-        <v>0.374</v>
+        <v>0.3740512733246232</v>
       </c>
       <c r="E318">
         <v>317</v>
@@ -79323,7 +79323,7 @@
         <v>0.35</v>
       </c>
       <c r="AR318">
-        <v>0.368</v>
+        <v>0.3680327500972012</v>
       </c>
       <c r="AS318">
         <v>322</v>
@@ -79458,7 +79458,7 @@
         </is>
       </c>
       <c r="D319">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E319">
         <v>318</v>
@@ -79572,7 +79572,7 @@
         <v>0.4</v>
       </c>
       <c r="AR319">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS319">
         <v>288</v>
@@ -79707,7 +79707,7 @@
         </is>
       </c>
       <c r="D320">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E320">
         <v>319</v>
@@ -79821,7 +79821,7 @@
         <v>0.4</v>
       </c>
       <c r="AR320">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS320">
         <v>332</v>
@@ -79956,7 +79956,7 @@
         </is>
       </c>
       <c r="D321">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E321">
         <v>320</v>
@@ -80070,7 +80070,7 @@
         <v>0.4</v>
       </c>
       <c r="AR321">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS321">
         <v>317</v>
@@ -80205,7 +80205,7 @@
         </is>
       </c>
       <c r="D322">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E322">
         <v>321</v>
@@ -80319,7 +80319,7 @@
         <v>0.4</v>
       </c>
       <c r="AR322">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS322">
         <v>251</v>
@@ -80454,7 +80454,7 @@
         </is>
       </c>
       <c r="D323">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E323">
         <v>322</v>
@@ -80568,7 +80568,7 @@
         <v>0.4</v>
       </c>
       <c r="AR323">
-        <v>0.339</v>
+        <v>0.3388875005639072</v>
       </c>
       <c r="AS323">
         <v>338</v>
@@ -80703,7 +80703,7 @@
         </is>
       </c>
       <c r="D324">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E324">
         <v>323</v>
@@ -80817,7 +80817,7 @@
         <v>0.4</v>
       </c>
       <c r="AR324">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS324">
         <v>279</v>
@@ -80952,7 +80952,7 @@
         </is>
       </c>
       <c r="D325">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E325">
         <v>324</v>
@@ -81066,7 +81066,7 @@
         <v>0.4</v>
       </c>
       <c r="AR325">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS325">
         <v>326</v>
@@ -81201,7 +81201,7 @@
         </is>
       </c>
       <c r="D326">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E326">
         <v>325</v>
@@ -81315,7 +81315,7 @@
         <v>0.4</v>
       </c>
       <c r="AR326">
-        <v>0.368</v>
+        <v>0.3680327500972012</v>
       </c>
       <c r="AS326">
         <v>323</v>
@@ -81450,7 +81450,7 @@
         </is>
       </c>
       <c r="D327">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E327">
         <v>326</v>
@@ -81564,7 +81564,7 @@
         <v>0.4</v>
       </c>
       <c r="AR327">
-        <v>0.4</v>
+        <v>0.4000925245838244</v>
       </c>
       <c r="AS327">
         <v>280</v>
@@ -81699,7 +81699,7 @@
         </is>
       </c>
       <c r="D328">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E328">
         <v>327</v>
@@ -81813,7 +81813,7 @@
         <v>0.4</v>
       </c>
       <c r="AR328">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS328">
         <v>310</v>
@@ -81948,7 +81948,7 @@
         </is>
       </c>
       <c r="D329">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E329">
         <v>328</v>
@@ -82062,7 +82062,7 @@
         <v>0.4</v>
       </c>
       <c r="AR329">
-        <v>0.461</v>
+        <v>0.4612975486037417</v>
       </c>
       <c r="AS329">
         <v>197</v>
@@ -82197,7 +82197,7 @@
         </is>
       </c>
       <c r="D330">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E330">
         <v>329</v>
@@ -82311,7 +82311,7 @@
         <v>0.4</v>
       </c>
       <c r="AR330">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS330">
         <v>313</v>
@@ -82446,7 +82446,7 @@
         </is>
       </c>
       <c r="D331">
-        <v>0.366</v>
+        <v>0.3660957694742377</v>
       </c>
       <c r="E331">
         <v>330</v>
@@ -82560,7 +82560,7 @@
         <v>0.4</v>
       </c>
       <c r="AR331">
-        <v>0.467</v>
+        <v>0.4671265985104004</v>
       </c>
       <c r="AS331">
         <v>195</v>
@@ -82695,7 +82695,7 @@
         </is>
       </c>
       <c r="D332">
-        <v>0.358</v>
+        <v>0.3581402656238522</v>
       </c>
       <c r="E332">
         <v>331</v>
@@ -82809,7 +82809,7 @@
         <v>0.45</v>
       </c>
       <c r="AR332">
-        <v>0.289</v>
+        <v>0.2893405763573075</v>
       </c>
       <c r="AS332">
         <v>342</v>
@@ -82944,7 +82944,7 @@
         </is>
       </c>
       <c r="D333">
-        <v>0.355</v>
+        <v>0.3554884310070571</v>
       </c>
       <c r="E333">
         <v>332</v>
@@ -83058,7 +83058,7 @@
         <v>0.3</v>
       </c>
       <c r="AR333">
-        <v>0.429</v>
+        <v>0.4292377741171184</v>
       </c>
       <c r="AS333">
         <v>245</v>
@@ -83193,7 +83193,7 @@
         </is>
       </c>
       <c r="D334">
-        <v>0.348</v>
+        <v>0.3475329271566715</v>
       </c>
       <c r="E334">
         <v>333</v>
@@ -83307,7 +83307,7 @@
         <v>0.35</v>
       </c>
       <c r="AR334">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS334">
         <v>318</v>
@@ -83442,7 +83442,7 @@
         </is>
       </c>
       <c r="D335">
-        <v>0.348</v>
+        <v>0.3475329271566715</v>
       </c>
       <c r="E335">
         <v>334</v>
@@ -83556,7 +83556,7 @@
         <v>0.35</v>
       </c>
       <c r="AR335">
-        <v>0.438</v>
+        <v>0.4379813489771065</v>
       </c>
       <c r="AS335">
         <v>231</v>
@@ -83691,7 +83691,7 @@
         </is>
       </c>
       <c r="D336">
-        <v>0.348</v>
+        <v>0.3475329271566715</v>
       </c>
       <c r="E336">
         <v>335</v>
@@ -83805,7 +83805,7 @@
         <v>0.35</v>
       </c>
       <c r="AR336">
-        <v>0.359</v>
+        <v>0.3592891752372129</v>
       </c>
       <c r="AS336">
         <v>328</v>
@@ -83940,7 +83940,7 @@
         </is>
       </c>
       <c r="D337">
-        <v>0.348</v>
+        <v>0.3475329271566715</v>
       </c>
       <c r="E337">
         <v>336</v>
@@ -84054,7 +84054,7 @@
         <v>0.35</v>
       </c>
       <c r="AR337">
-        <v>0.33</v>
+        <v>0.330143925703919</v>
       </c>
       <c r="AS337">
         <v>340</v>
@@ -84189,7 +84189,7 @@
         </is>
       </c>
       <c r="D338">
-        <v>0.348</v>
+        <v>0.3475329271566715</v>
       </c>
       <c r="E338">
         <v>337</v>
@@ -84303,7 +84303,7 @@
         <v>0.35</v>
       </c>
       <c r="AR338">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS338">
         <v>256</v>
@@ -84438,7 +84438,7 @@
         </is>
       </c>
       <c r="D339">
-        <v>0.337</v>
+        <v>0.3369255886894909</v>
       </c>
       <c r="E339">
         <v>338</v>
@@ -84552,7 +84552,7 @@
         <v>0.25</v>
       </c>
       <c r="AR339">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS339">
         <v>308</v>
@@ -84687,7 +84687,7 @@
         </is>
       </c>
       <c r="D340">
-        <v>0.337</v>
+        <v>0.3369255886894909</v>
       </c>
       <c r="E340">
         <v>339</v>
@@ -84801,7 +84801,7 @@
         <v>0.25</v>
       </c>
       <c r="AR340">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS340">
         <v>303</v>
@@ -84936,7 +84936,7 @@
         </is>
       </c>
       <c r="D341">
-        <v>0.329</v>
+        <v>0.3289700848391054</v>
       </c>
       <c r="E341">
         <v>340</v>
@@ -85050,7 +85050,7 @@
         <v>0.3</v>
       </c>
       <c r="AR341">
-        <v>0.388</v>
+        <v>0.3884344247705069</v>
       </c>
       <c r="AS341">
         <v>299</v>
@@ -85185,7 +85185,7 @@
         </is>
       </c>
       <c r="D342">
-        <v>0.321</v>
+        <v>0.3210145809887198</v>
       </c>
       <c r="E342">
         <v>341</v>
@@ -85299,7 +85299,7 @@
         <v>0.35</v>
       </c>
       <c r="AR342">
-        <v>0.368</v>
+        <v>0.3680327500972012</v>
       </c>
       <c r="AS342">
         <v>324</v>
@@ -85434,7 +85434,7 @@
         </is>
       </c>
       <c r="D343">
-        <v>0.31</v>
+        <v>0.3104072425215392</v>
       </c>
       <c r="E343">
         <v>342</v>
@@ -85548,7 +85548,7 @@
         <v>0.25</v>
       </c>
       <c r="AR343">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS343">
         <v>261</v>
@@ -85683,7 +85683,7 @@
         </is>
       </c>
       <c r="D344">
-        <v>0.292</v>
+        <v>0.2918444002039731</v>
       </c>
       <c r="E344">
         <v>343</v>
@@ -85797,7 +85797,7 @@
         <v>0.2</v>
       </c>
       <c r="AR344">
-        <v>0.42</v>
+        <v>0.4204941992571302</v>
       </c>
       <c r="AS344">
         <v>266</v>
@@ -85932,7 +85932,7 @@
         </is>
       </c>
       <c r="D345">
-        <v>0.255</v>
+        <v>0.2547187155688406</v>
       </c>
       <c r="E345">
         <v>344</v>
@@ -86067,7 +86067,7 @@
         </is>
       </c>
       <c r="D346">
-        <v>0.191</v>
+        <v>0.1910746847657567</v>
       </c>
       <c r="E346">
         <v>345</v>
@@ -86181,7 +86181,7 @@
         <v>0</v>
       </c>
       <c r="AR346">
-        <v>0.38</v>
+        <v>0.3796908499105187</v>
       </c>
       <c r="AS346">
         <v>316</v>
